--- a/PPREstimation/output/top10/36_1_South_China_Sea_SCS-2007_Northern_South_China_Sea_(2000s).xlsx
+++ b/PPREstimation/output/top10/36_1_South_China_Sea_SCS-2007_Northern_South_China_Sea_(2000s).xlsx
@@ -701,7 +701,11 @@
           <t>DET</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr"/>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Non-living detritus.</t>
+        </is>
+      </c>
       <c r="F3" s="2" t="n">
         <v>1</v>
       </c>
@@ -785,7 +789,11 @@
           <t>Regular</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Marine turtles; no species list documented.</t>
+        </is>
+      </c>
       <c r="F4" s="2" t="n">
         <v>2.972461641294619</v>
       </c>
@@ -869,7 +877,11 @@
           <t>Regular</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Other marine mammals; no species list documented.</t>
+        </is>
+      </c>
       <c r="F5" s="2" t="n">
         <v>3.922805246334676</v>
       </c>
@@ -953,7 +965,11 @@
           <t>Regular</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr"/>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Pinnipeds; no species list documented.</t>
+        </is>
+      </c>
       <c r="F6" s="2" t="n">
         <v>4.146384704092291</v>
       </c>
@@ -1037,7 +1053,11 @@
           <t>Regular</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr"/>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Seabirds; no species list documented.</t>
+        </is>
+      </c>
       <c r="F7" s="2" t="n">
         <v>3.414700950377541</v>
       </c>
@@ -1121,7 +1141,11 @@
           <t>Regular</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr"/>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Pelagic elasmobranchs. No species list documented.</t>
+        </is>
+      </c>
       <c r="F8" s="2" t="n">
         <v>3.989708938669605</v>
       </c>
@@ -1205,7 +1229,11 @@
           <t>Regular</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr"/>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Demersal elasmobranchs. No species list documented.</t>
+        </is>
+      </c>
       <c r="F9" s="2" t="n">
         <v>3.509427430945212</v>
       </c>
@@ -1289,7 +1317,11 @@
           <t>Regular</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr"/>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Pelagic fish with maximum total length &gt;30 cm, adult stanza from 18 months; includes scombrids.</t>
+        </is>
+      </c>
       <c r="F10" s="2" t="n">
         <v>3.367201063009562</v>
       </c>
@@ -1373,7 +1405,11 @@
           <t>Regular</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr"/>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Pelagic fish with maximum total length &gt;30 cm, juvenile stanza; source paragraph mistakenly says demersal, but heading, examples and stanza names establish pelagic.</t>
+        </is>
+      </c>
       <c r="F11" s="2" t="n">
         <v>2.893396853714223</v>
       </c>
@@ -1457,7 +1493,11 @@
           <t>Regular</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Pelagic fish with maximum total length &lt;=30 cm, including sardines, thryssa and anchovies.</t>
+        </is>
+      </c>
       <c r="F12" s="2" t="n">
         <v>2.781666666666666</v>
       </c>
@@ -1541,7 +1581,11 @@
           <t>Regular</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr"/>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Psenopsis anomala; definition: Psenopsis anomala.</t>
+        </is>
+      </c>
       <c r="F13" s="2" t="n">
         <v>3.03486548350679</v>
       </c>
@@ -1625,7 +1669,11 @@
           <t>Regular</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr"/>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Final table has one Benthopelagic fish group. Appendix separately describes small &lt;=30 cm and large &gt;30 cm benthopelagic fish; their relationship to the final single pool is not resolved.</t>
+        </is>
+      </c>
       <c r="F14" s="2" t="n">
         <v>2.780602456126404</v>
       </c>
@@ -1709,7 +1757,11 @@
           <t>Regular</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr"/>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Demersal fish with maximum total length &gt;30 cm, adult stanza from 18 months; dedicated groups excluded.</t>
+        </is>
+      </c>
       <c r="F15" s="2" t="n">
         <v>3.427086988746579</v>
       </c>
@@ -1793,7 +1845,11 @@
           <t>Regular</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr"/>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Demersal fish with maximum total length &gt;30 cm, juvenile stanza; dedicated groups excluded.</t>
+        </is>
+      </c>
       <c r="F16" s="2" t="n">
         <v>3.043612179667134</v>
       </c>
@@ -1877,7 +1933,11 @@
           <t>Regular</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr"/>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Demersal fish with maximum total length &lt;=30 cm, except taxa in dedicated groups.</t>
+        </is>
+      </c>
       <c r="F17" s="2" t="n">
         <v>3.00931693541396</v>
       </c>
@@ -1961,7 +2021,11 @@
           <t>Regular</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr"/>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Larimichthys crocea; definition: Large Sciaenidae &gt;30 cm maximum length, adult fish from 24 months.</t>
+        </is>
+      </c>
       <c r="F18" s="2" t="n">
         <v>3.472838939946794</v>
       </c>
@@ -2045,7 +2109,11 @@
           <t>Regular</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr"/>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Larimichthys crocea; definition: Large Sciaenidae &gt;30 cm maximum length, immature fish younger than 24 months.</t>
+        </is>
+      </c>
       <c r="F19" s="2" t="n">
         <v>3.238588184699975</v>
       </c>
@@ -2129,7 +2197,11 @@
           <t>Regular</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr"/>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Agyrosomus spp.; Pennahia spp.; Pennahia (Agyrosomus) argentatus; definition: Small Sciaenidae &lt;=30 cm; Pennahia is explicitly listed despite differing SAU size classes.</t>
+        </is>
+      </c>
       <c r="F20" s="2" t="n">
         <v>3.312753045334324</v>
       </c>
@@ -2213,7 +2285,11 @@
           <t>Regular</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr"/>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Family Serranidae; the final table calls this Adult groupers but supplies no separate juvenile grouper compartment.</t>
+        </is>
+      </c>
       <c r="F21" s="2" t="n">
         <v>3.759047426500872</v>
       </c>
@@ -2297,7 +2373,11 @@
           <t>Regular</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr"/>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Family Lutjanidae.</t>
+        </is>
+      </c>
       <c r="F22" s="2" t="n">
         <v>3.769209176753436</v>
       </c>
@@ -2381,7 +2461,11 @@
           <t>Regular</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr"/>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Family Stromateidae. Other pomfret-like families are excluded from the stated taxonomic definition.</t>
+        </is>
+      </c>
       <c r="F23" s="2" t="n">
         <v>3.587017325582895</v>
       </c>
@@ -2465,7 +2549,11 @@
           <t>Regular</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr"/>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Trichiurus lepturus; definition: Family Trichiuridae, adult stanza from 18 months.</t>
+        </is>
+      </c>
       <c r="F24" s="2" t="n">
         <v>3.913681634309746</v>
       </c>
@@ -2549,7 +2637,11 @@
           <t>Regular</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr"/>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Trichiurus lepturus; definition: Family Trichiuridae, juvenile stanza younger than 18 months.</t>
+        </is>
+      </c>
       <c r="F25" s="2" t="n">
         <v>3.878329620318159</v>
       </c>
@@ -2633,7 +2725,11 @@
           <t>Regular</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr"/>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Saurida tumbil; S. undosquamis; definition: Family Synodontidae.</t>
+        </is>
+      </c>
       <c r="F26" s="2" t="n">
         <v>3.856614847729229</v>
       </c>
@@ -2717,7 +2813,11 @@
           <t>Regular</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr"/>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Family Priacanthidae.</t>
+        </is>
+      </c>
       <c r="F27" s="2" t="n">
         <v>3.471984562385465</v>
       </c>
@@ -2801,7 +2901,11 @@
           <t>Regular</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr"/>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Nemipterus virgatus; N. bathybius; N. japonicus; definition: Family Nemipteridae.</t>
+        </is>
+      </c>
       <c r="F28" s="2" t="n">
         <v>3.210667554973283</v>
       </c>
@@ -2885,7 +2989,11 @@
           <t>Regular</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr"/>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Loligo edulis; L. chinensis; definition: Cephalopoda, dominated by Loligo squid.</t>
+        </is>
+      </c>
       <c r="F29" s="2" t="n">
         <v>3.29081348223872</v>
       </c>
@@ -2969,7 +3077,11 @@
           <t>Regular</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr"/>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Crabs.</t>
+        </is>
+      </c>
       <c r="F30" s="2" t="n">
         <v>2.523917480221986</v>
       </c>
@@ -3053,7 +3165,11 @@
           <t>Regular</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr"/>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Metapenaeopsis palmensis; M. barbata; definition: Shrimps including penaeids; Acetes is explicitly in Zooplankton.</t>
+        </is>
+      </c>
       <c r="F31" s="2" t="n">
         <v>2.314</v>
       </c>
@@ -3137,7 +3253,11 @@
           <t>Regular</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr"/>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Sessile and other invertebrates, separate from polychaetes, echinoderms, crustaceans and molluscs.</t>
+        </is>
+      </c>
       <c r="F32" s="2" t="n">
         <v>2.6</v>
       </c>
@@ -3221,7 +3341,11 @@
           <t>Regular</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr"/>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Non-cephalopod Mollusca.</t>
+        </is>
+      </c>
       <c r="F33" s="2" t="n">
         <v>2.177777777777778</v>
       </c>
@@ -3305,7 +3429,11 @@
           <t>Regular</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr"/>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Benthic crustaceans excluding shrimps and crabs; Oratosquilla spp. supplies the P/B estimate.</t>
+        </is>
+      </c>
       <c r="F34" s="2" t="n">
         <v>2.199822222222222</v>
       </c>
@@ -3389,7 +3517,11 @@
           <t>Regular</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr"/>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Echinodermata.</t>
+        </is>
+      </c>
       <c r="F35" s="2" t="n">
         <v>2.333214688865273</v>
       </c>
@@ -3473,7 +3605,11 @@
           <t>Regular</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr"/>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Polychaeta.</t>
+        </is>
+      </c>
       <c r="F36" s="2" t="n">
         <v>2</v>
       </c>
@@ -3557,7 +3693,11 @@
           <t>Regular</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr"/>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Medusae of Cnidaria.</t>
+        </is>
+      </c>
       <c r="F37" s="2" t="n">
         <v>3.104070721217805</v>
       </c>
@@ -3641,7 +3781,11 @@
           <t>Regular</t>
         </is>
       </c>
-      <c r="E38" t="inlineStr"/>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Acetes spp.; definition: Zooplankton; explicitly includes the landed Mo shrimp Acetes spp.</t>
+        </is>
+      </c>
       <c r="F38" s="2" t="n">
         <v>2</v>
       </c>
@@ -3725,7 +3869,11 @@
           <t>PP</t>
         </is>
       </c>
-      <c r="E39" t="inlineStr"/>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Benthic algae.</t>
+        </is>
+      </c>
       <c r="F39" s="2" t="n">
         <v>1</v>
       </c>
@@ -3809,7 +3957,11 @@
           <t>PP</t>
         </is>
       </c>
-      <c r="E40" t="inlineStr"/>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Phytoplankton dominated by diatoms, followed by dinoflagellates.</t>
+        </is>
+      </c>
       <c r="F40" s="2" t="n">
         <v>1</v>
       </c>
@@ -4204,10 +4356,10 @@
         <v>182.1811442177236</v>
       </c>
       <c r="U4" s="2" t="n">
-        <v>440.3846821898635</v>
+        <v>434.870726158594</v>
       </c>
       <c r="V4" s="2" t="n">
-        <v>13666.97612853732</v>
+        <v>14268.62512307632</v>
       </c>
     </row>
     <row r="5">
@@ -4268,10 +4420,10 @@
         <v>952.6553407052243</v>
       </c>
       <c r="U5" s="2" t="n">
-        <v>2209.517373810315</v>
+        <v>2194.112594110687</v>
       </c>
       <c r="V5" s="2" t="n">
-        <v>573572.3510982507</v>
+        <v>592776.6105618178</v>
       </c>
     </row>
     <row r="6">
@@ -4332,10 +4484,10 @@
         <v>2900.402531206196</v>
       </c>
       <c r="U6" s="2" t="n">
-        <v>7281.280994289177</v>
+        <v>7257.644075546664</v>
       </c>
       <c r="V6" s="2" t="n">
-        <v>237044.8858084446</v>
+        <v>239328.6672069039</v>
       </c>
     </row>
     <row r="7">
@@ -4396,10 +4548,10 @@
         <v>5372.039527145474</v>
       </c>
       <c r="U7" s="2" t="n">
-        <v>12605.47825810749</v>
+        <v>12426.71486470108</v>
       </c>
       <c r="V7" s="2" t="n">
-        <v>2626163.57596226</v>
+        <v>2710824.468534396</v>
       </c>
     </row>
     <row r="8">
@@ -4460,10 +4612,10 @@
         <v>53.93747956144836</v>
       </c>
       <c r="U8" s="2" t="n">
-        <v>126.0409967771675</v>
+        <v>127.7782897929655</v>
       </c>
       <c r="V8" s="2" t="n">
-        <v>3132.97225969056</v>
+        <v>3261.887236450888</v>
       </c>
     </row>
     <row r="9">
@@ -4524,10 +4676,10 @@
         <v>23.78827723896387</v>
       </c>
       <c r="U9" s="2" t="n">
-        <v>56.3881409681218</v>
+        <v>57.1223130247557</v>
       </c>
       <c r="V9" s="2" t="n">
-        <v>469.4025002467295</v>
+        <v>481.4152786051081</v>
       </c>
     </row>
     <row r="10">
@@ -4588,10 +4740,10 @@
         <v>21.57939178002374</v>
       </c>
       <c r="U10" s="2" t="n">
-        <v>42.18268359827529</v>
+        <v>40.88393676289211</v>
       </c>
       <c r="V10" s="2" t="n">
-        <v>302.1410338003774</v>
+        <v>297.2156696521085</v>
       </c>
     </row>
     <row r="11">
@@ -4652,10 +4804,10 @@
         <v>11.30402238693303</v>
       </c>
       <c r="U11" s="2" t="n">
-        <v>20.09120661440291</v>
+        <v>20.54521502927857</v>
       </c>
       <c r="V11" s="2" t="n">
-        <v>165.5797803702818</v>
+        <v>170.3826290998149</v>
       </c>
     </row>
     <row r="12">
@@ -4716,10 +4868,10 @@
         <v>8.864132984123994</v>
       </c>
       <c r="U12" s="2" t="n">
-        <v>13.66968665992541</v>
+        <v>13.70380404870684</v>
       </c>
       <c r="V12" s="2" t="n">
-        <v>58.84286123362182</v>
+        <v>59.62843795395747</v>
       </c>
     </row>
     <row r="13">
@@ -4780,10 +4932,10 @@
         <v>29.8196909080155</v>
       </c>
       <c r="U13" s="2" t="n">
-        <v>50.76015343188091</v>
+        <v>51.77566532199707</v>
       </c>
       <c r="V13" s="2" t="n">
-        <v>272.3765577143959</v>
+        <v>277.6455928826152</v>
       </c>
     </row>
     <row r="14">
@@ -4844,10 +4996,10 @@
         <v>11.93362030374893</v>
       </c>
       <c r="U14" s="2" t="n">
-        <v>20.42037436994749</v>
+        <v>20.59473589721628</v>
       </c>
       <c r="V14" s="2" t="n">
-        <v>178.6637538061026</v>
+        <v>182.4550943026635</v>
       </c>
     </row>
     <row r="15">
@@ -4908,10 +5060,10 @@
         <v>11.91431322698926</v>
       </c>
       <c r="U15" s="2" t="n">
-        <v>27.67894560844614</v>
+        <v>27.89971284408954</v>
       </c>
       <c r="V15" s="2" t="n">
-        <v>266.846243608347</v>
+        <v>274.6700836649002</v>
       </c>
     </row>
     <row r="16">
@@ -4972,10 +5124,10 @@
         <v>11.4575331689114</v>
       </c>
       <c r="U16" s="2" t="n">
-        <v>21.14007867021758</v>
+        <v>20.93443443774935</v>
       </c>
       <c r="V16" s="2" t="n">
-        <v>155.5209786358109</v>
+        <v>157.9956322191315</v>
       </c>
     </row>
     <row r="17">
@@ -5036,10 +5188,10 @@
         <v>11.11590482324036</v>
       </c>
       <c r="U17" s="2" t="n">
-        <v>21.01282745955882</v>
+        <v>21.19115126970615</v>
       </c>
       <c r="V17" s="2" t="n">
-        <v>119.7628952567189</v>
+        <v>123.5309737289706</v>
       </c>
     </row>
     <row r="18">
@@ -5100,10 +5252,10 @@
         <v>24.41762899147337</v>
       </c>
       <c r="U18" s="2" t="n">
-        <v>52.95736470936264</v>
+        <v>53.34085803903789</v>
       </c>
       <c r="V18" s="2" t="n">
-        <v>646.8051686078903</v>
+        <v>656.1652444063013</v>
       </c>
     </row>
     <row r="19">
@@ -5164,10 +5316,10 @@
         <v>14.9141054812379</v>
       </c>
       <c r="U19" s="2" t="n">
-        <v>31.17747986634595</v>
+        <v>31.78197679499574</v>
       </c>
       <c r="V19" s="2" t="n">
-        <v>372.9140997312173</v>
+        <v>375.6377875876929</v>
       </c>
     </row>
     <row r="20">
@@ -5228,10 +5380,10 @@
         <v>13.09764712824062</v>
       </c>
       <c r="U20" s="2" t="n">
-        <v>27.27186391888887</v>
+        <v>26.97433607194651</v>
       </c>
       <c r="V20" s="2" t="n">
-        <v>175.9256608244542</v>
+        <v>177.9954044605451</v>
       </c>
     </row>
     <row r="21">
@@ -5292,10 +5444,10 @@
         <v>20.94658404970042</v>
       </c>
       <c r="U21" s="2" t="n">
-        <v>51.01415431313578</v>
+        <v>50.17483514895786</v>
       </c>
       <c r="V21" s="2" t="n">
-        <v>390.9373729254235</v>
+        <v>393.8993581467373</v>
       </c>
     </row>
     <row r="22">
@@ -5356,10 +5508,10 @@
         <v>34.31833246078967</v>
       </c>
       <c r="U22" s="2" t="n">
-        <v>79.37579163330342</v>
+        <v>79.92240479660268</v>
       </c>
       <c r="V22" s="2" t="n">
-        <v>473.1204296357511</v>
+        <v>493.283286347489</v>
       </c>
     </row>
     <row r="23">
@@ -5420,10 +5572,10 @@
         <v>35.01803010406012</v>
       </c>
       <c r="U23" s="2" t="n">
-        <v>73.62627205934726</v>
+        <v>75.71575224469092</v>
       </c>
       <c r="V23" s="2" t="n">
-        <v>844.4909984841072</v>
+        <v>855.8237626207754</v>
       </c>
     </row>
     <row r="24">
@@ -5484,10 +5636,10 @@
         <v>35.13329924401207</v>
       </c>
       <c r="U24" s="2" t="n">
-        <v>81.49178385541312</v>
+        <v>82.6201726054865</v>
       </c>
       <c r="V24" s="2" t="n">
-        <v>1269.953037775279</v>
+        <v>1295.392531013809</v>
       </c>
     </row>
     <row r="25">
@@ -5548,10 +5700,10 @@
         <v>38.80145517397714</v>
       </c>
       <c r="U25" s="2" t="n">
-        <v>93.45663250170895</v>
+        <v>94.12552996959936</v>
       </c>
       <c r="V25" s="2" t="n">
-        <v>1165.45246583885</v>
+        <v>1224.427483263716</v>
       </c>
     </row>
     <row r="26">
@@ -5612,10 +5764,10 @@
         <v>24.01341241735314</v>
       </c>
       <c r="U26" s="2" t="n">
-        <v>53.9918535584065</v>
+        <v>55.93589761954036</v>
       </c>
       <c r="V26" s="2" t="n">
-        <v>626.5155349317358</v>
+        <v>644.6692788100942</v>
       </c>
     </row>
     <row r="27">
@@ -5676,10 +5828,10 @@
         <v>15.42784343047193</v>
       </c>
       <c r="U27" s="2" t="n">
-        <v>35.80134644020516</v>
+        <v>34.97499602242549</v>
       </c>
       <c r="V27" s="2" t="n">
-        <v>366.5561754283211</v>
+        <v>377.6008816923421</v>
       </c>
     </row>
     <row r="28">
@@ -5740,10 +5892,10 @@
         <v>11.22514225228905</v>
       </c>
       <c r="U28" s="2" t="n">
-        <v>23.76503561821901</v>
+        <v>24.36337627644819</v>
       </c>
       <c r="V28" s="2" t="n">
-        <v>160.8732748828948</v>
+        <v>163.0380458625788</v>
       </c>
     </row>
     <row r="29">
@@ -5804,10 +5956,10 @@
         <v>9.837539249724486</v>
       </c>
       <c r="U29" s="2" t="n">
-        <v>19.34526521013256</v>
+        <v>19.76344489422008</v>
       </c>
       <c r="V29" s="2" t="n">
-        <v>377.1270445600881</v>
+        <v>393.3544196533529</v>
       </c>
     </row>
     <row r="30">
@@ -5868,10 +6020,10 @@
         <v>2.466445302327833</v>
       </c>
       <c r="U30" s="2" t="n">
-        <v>4.575432927905404</v>
+        <v>4.517853299786299</v>
       </c>
       <c r="V30" s="2" t="n">
-        <v>22.26562506775525</v>
+        <v>21.98289703467697</v>
       </c>
     </row>
     <row r="31">
@@ -5932,10 +6084,10 @@
         <v>2.438514863157878</v>
       </c>
       <c r="U31" s="2" t="n">
-        <v>3.657465442569894</v>
+        <v>3.743903260880651</v>
       </c>
       <c r="V31" s="2" t="n">
-        <v>11.51680036342317</v>
+        <v>11.53011267098982</v>
       </c>
     </row>
     <row r="32">
@@ -5996,10 +6148,10 @@
         <v>14.5152</v>
       </c>
       <c r="U32" s="2" t="n">
-        <v>23.27200686430079</v>
+        <v>23.29619952216411</v>
       </c>
       <c r="V32" s="2" t="n">
-        <v>131.5506281205234</v>
+        <v>135.0015100252899</v>
       </c>
     </row>
     <row r="33">
@@ -6060,10 +6212,10 @@
         <v>1.467726256458431</v>
       </c>
       <c r="U33" s="2" t="n">
-        <v>2.316468136076529</v>
+        <v>2.339497017221834</v>
       </c>
       <c r="V33" s="2" t="n">
-        <v>8.211436187062942</v>
+        <v>8.332893762949299</v>
       </c>
     </row>
     <row r="34">
@@ -6124,10 +6276,10 @@
         <v>1.984156571171458</v>
       </c>
       <c r="U34" s="2" t="n">
-        <v>3.078440865974815</v>
+        <v>3.109492389501218</v>
       </c>
       <c r="V34" s="2" t="n">
-        <v>13.4614700967153</v>
+        <v>13.43459325370352</v>
       </c>
     </row>
     <row r="35">
@@ -6188,10 +6340,10 @@
         <v>5.8521606491946</v>
       </c>
       <c r="U35" s="2" t="n">
-        <v>11.24357706972218</v>
+        <v>11.05839127716684</v>
       </c>
       <c r="V35" s="2" t="n">
-        <v>162.5801052871297</v>
+        <v>165.5161776883501</v>
       </c>
     </row>
     <row r="36">
@@ -6316,10 +6468,10 @@
         <v>13.77945182402281</v>
       </c>
       <c r="U37" s="2" t="n">
-        <v>24.0502521865533</v>
+        <v>24.70282034171536</v>
       </c>
       <c r="V37" s="2" t="n">
-        <v>296.2230801303305</v>
+        <v>299.6641780113497</v>
       </c>
     </row>
     <row r="38">
@@ -6380,10 +6532,10 @@
         <v>3.36</v>
       </c>
       <c r="U38" s="2" t="n">
-        <v>4.162323183415872</v>
+        <v>4.26431220827355</v>
       </c>
       <c r="V38" s="2" t="n">
-        <v>13.83784092310692</v>
+        <v>14.20866587077268</v>
       </c>
     </row>
     <row r="39">
@@ -6792,10 +6944,10 @@
         <v>1.008629161958598</v>
       </c>
       <c r="U3" s="2" t="n">
-        <v>1.007752776423084</v>
+        <v>1.008016146229588</v>
       </c>
       <c r="V3" s="2" t="n">
-        <v>0.995222499887902</v>
+        <v>0.9952224998879019</v>
       </c>
     </row>
     <row r="4">
@@ -6862,10 +7014,10 @@
         <v>304.3332323568129</v>
       </c>
       <c r="U4" s="2" t="n">
-        <v>752.5624523165404</v>
+        <v>742.1649659561815</v>
       </c>
       <c r="V4" s="2" t="n">
-        <v>20802.4326168081</v>
+        <v>21695.25266434331</v>
       </c>
     </row>
     <row r="5">
@@ -6932,10 +7084,10 @@
         <v>1492.975981078933</v>
       </c>
       <c r="U5" s="2" t="n">
-        <v>3498.089216485562</v>
+        <v>3469.628719321709</v>
       </c>
       <c r="V5" s="2" t="n">
-        <v>851200.3935775722</v>
+        <v>879139.5075075517</v>
       </c>
     </row>
     <row r="6">
@@ -7002,10 +7154,10 @@
         <v>5428.429196523921</v>
       </c>
       <c r="U6" s="2" t="n">
-        <v>13491.47359542066</v>
+        <v>13423.92335965779</v>
       </c>
       <c r="V6" s="2" t="n">
-        <v>365406.3095555897</v>
+        <v>368249.9207858762</v>
       </c>
     </row>
     <row r="7">
@@ -7072,10 +7224,10 @@
         <v>9568.831724452888</v>
       </c>
       <c r="U7" s="2" t="n">
-        <v>22080.98332526741</v>
+        <v>21735.71582340555</v>
       </c>
       <c r="V7" s="2" t="n">
-        <v>3981241.544519183</v>
+        <v>4104229.031155468</v>
       </c>
     </row>
     <row r="8">
@@ -7142,10 +7294,10 @@
         <v>82.32322944213459</v>
       </c>
       <c r="U8" s="2" t="n">
-        <v>194.2386505453485</v>
+        <v>196.7045734834864</v>
       </c>
       <c r="V8" s="2" t="n">
-        <v>4686.07721294298</v>
+        <v>4875.473380713382</v>
       </c>
     </row>
     <row r="9">
@@ -7212,10 +7364,10 @@
         <v>50.00067972328989</v>
       </c>
       <c r="U9" s="2" t="n">
-        <v>115.2884559238654</v>
+        <v>116.3771315428858</v>
       </c>
       <c r="V9" s="2" t="n">
-        <v>756.4086308488268</v>
+        <v>773.5898693229019</v>
       </c>
     </row>
     <row r="10">
@@ -7282,10 +7434,10 @@
         <v>32.18844881440729</v>
       </c>
       <c r="U10" s="2" t="n">
-        <v>63.33657414094962</v>
+        <v>61.38323918231102</v>
       </c>
       <c r="V10" s="2" t="n">
-        <v>443.4751538077708</v>
+        <v>436.0900935006518</v>
       </c>
     </row>
     <row r="11">
@@ -7352,10 +7504,10 @@
         <v>17.21811430080176</v>
       </c>
       <c r="U11" s="2" t="n">
-        <v>30.70793432881509</v>
+        <v>31.37764895818272</v>
       </c>
       <c r="V11" s="2" t="n">
-        <v>243.6943185809622</v>
+        <v>250.6349616303636</v>
       </c>
     </row>
     <row r="12">
@@ -7422,10 +7574,10 @@
         <v>12.62464148874943</v>
       </c>
       <c r="U12" s="2" t="n">
-        <v>19.56725046656314</v>
+        <v>19.62196367199751</v>
       </c>
       <c r="V12" s="2" t="n">
-        <v>84.14671703747628</v>
+        <v>85.28246102658841</v>
       </c>
     </row>
     <row r="13">
@@ -7492,10 +7644,10 @@
         <v>44.47333251218827</v>
       </c>
       <c r="U13" s="2" t="n">
-        <v>76.02720668617863</v>
+        <v>77.49397502374835</v>
       </c>
       <c r="V13" s="2" t="n">
-        <v>398.5060770083255</v>
+        <v>406.0871436305475</v>
       </c>
     </row>
     <row r="14">
@@ -7562,10 +7714,10 @@
         <v>18.05777036079494</v>
       </c>
       <c r="U14" s="2" t="n">
-        <v>31.2819986133635</v>
+        <v>31.54192802989084</v>
       </c>
       <c r="V14" s="2" t="n">
-        <v>264.4713644926504</v>
+        <v>269.9119415904116</v>
       </c>
     </row>
     <row r="15">
@@ -7632,10 +7784,10 @@
         <v>26.00586422754296</v>
       </c>
       <c r="U15" s="2" t="n">
-        <v>58.24381920311886</v>
+        <v>58.59712637972502</v>
       </c>
       <c r="V15" s="2" t="n">
-        <v>433.0802015836003</v>
+        <v>444.5706447547481</v>
       </c>
     </row>
     <row r="16">
@@ -7702,10 +7854,10 @@
         <v>21.72005085282455</v>
       </c>
       <c r="U16" s="2" t="n">
-        <v>39.78267862258517</v>
+        <v>39.33017180038939</v>
       </c>
       <c r="V16" s="2" t="n">
-        <v>246.2104582914199</v>
+        <v>249.53562033654</v>
       </c>
     </row>
     <row r="17">
@@ -7772,10 +7924,10 @@
         <v>22.82774046680624</v>
       </c>
       <c r="U17" s="2" t="n">
-        <v>42.51121833485472</v>
+        <v>42.76342839301487</v>
       </c>
       <c r="V17" s="2" t="n">
-        <v>193.8368982482251</v>
+        <v>199.476508548944</v>
       </c>
     </row>
     <row r="18">
@@ -7842,10 +7994,10 @@
         <v>42.9922604911004</v>
       </c>
       <c r="U18" s="2" t="n">
-        <v>92.53618333706638</v>
+        <v>93.04425288505252</v>
       </c>
       <c r="V18" s="2" t="n">
-        <v>984.3859855664418</v>
+        <v>997.5740475825862</v>
       </c>
     </row>
     <row r="19">
@@ -7912,10 +8064,10 @@
         <v>29.8238831557871</v>
       </c>
       <c r="U19" s="2" t="n">
-        <v>61.15545970131198</v>
+        <v>62.27657087196675</v>
       </c>
       <c r="V19" s="2" t="n">
-        <v>591.37642032851</v>
+        <v>594.4319588755127</v>
       </c>
     </row>
     <row r="20">
@@ -7982,10 +8134,10 @@
         <v>24.05207048768307</v>
       </c>
       <c r="U20" s="2" t="n">
-        <v>49.84573562743678</v>
+        <v>49.22277453393004</v>
       </c>
       <c r="V20" s="2" t="n">
-        <v>273.6884737488751</v>
+        <v>276.4589585725923</v>
       </c>
     </row>
     <row r="21">
@@ -8052,10 +8204,10 @@
         <v>43.9071954720966</v>
       </c>
       <c r="U21" s="2" t="n">
-        <v>104.3874999205393</v>
+        <v>102.3702816000078</v>
       </c>
       <c r="V21" s="2" t="n">
-        <v>624.1816559668533</v>
+        <v>627.3528167669332</v>
       </c>
     </row>
     <row r="22">
@@ -8122,10 +8274,10 @@
         <v>72.17779039044444</v>
       </c>
       <c r="U22" s="2" t="n">
-        <v>163.7954589295572</v>
+        <v>164.3907432483787</v>
       </c>
       <c r="V22" s="2" t="n">
-        <v>772.1359861133358</v>
+        <v>802.6979220092956</v>
       </c>
     </row>
     <row r="23">
@@ -8192,10 +8344,10 @@
         <v>51.42698729019422</v>
       </c>
       <c r="U23" s="2" t="n">
-        <v>107.8785886623308</v>
+        <v>110.8757957759221</v>
       </c>
       <c r="V23" s="2" t="n">
-        <v>1210.563065296902</v>
+        <v>1226.777069878792</v>
       </c>
     </row>
     <row r="24">
@@ -8262,10 +8414,10 @@
         <v>59.46878459014955</v>
       </c>
       <c r="U24" s="2" t="n">
-        <v>139.4752327032504</v>
+        <v>141.2973145864974</v>
       </c>
       <c r="V24" s="2" t="n">
-        <v>1932.647762735833</v>
+        <v>1969.265633804265</v>
       </c>
     </row>
     <row r="25">
@@ -8332,10 +8484,10 @@
         <v>70.93288291178348</v>
       </c>
       <c r="U25" s="2" t="n">
-        <v>170.3225231059668</v>
+        <v>171.2799446802703</v>
       </c>
       <c r="V25" s="2" t="n">
-        <v>1792.439430629529</v>
+        <v>1880.403394533115</v>
       </c>
     </row>
     <row r="26">
@@ -8402,10 +8554,10 @@
         <v>42.72445537308758</v>
       </c>
       <c r="U26" s="2" t="n">
-        <v>96.67541833104535</v>
+        <v>100.0490874662719</v>
       </c>
       <c r="V26" s="2" t="n">
-        <v>967.9914262949476</v>
+        <v>994.6946215783587</v>
       </c>
     </row>
     <row r="27">
@@ -8472,10 +8624,10 @@
         <v>31.5801549832506</v>
       </c>
       <c r="U27" s="2" t="n">
-        <v>72.52531821610054</v>
+        <v>70.66568663288975</v>
       </c>
       <c r="V27" s="2" t="n">
-        <v>593.6721562571793</v>
+        <v>610.0540138948419</v>
       </c>
     </row>
     <row r="28">
@@ -8542,10 +8694,10 @@
         <v>26.38915679194307</v>
       </c>
       <c r="U28" s="2" t="n">
-        <v>53.46667087865562</v>
+        <v>54.74518716987259</v>
       </c>
       <c r="V28" s="2" t="n">
-        <v>268.2617879872659</v>
+        <v>271.3129782298061</v>
       </c>
     </row>
     <row r="29">
@@ -8612,10 +8764,10 @@
         <v>16.10003412407702</v>
       </c>
       <c r="U29" s="2" t="n">
-        <v>31.69560108931946</v>
+        <v>32.32843994658725</v>
       </c>
       <c r="V29" s="2" t="n">
-        <v>564.2980549967825</v>
+        <v>587.9816292505517</v>
       </c>
     </row>
     <row r="30">
@@ -8682,10 +8834,10 @@
         <v>8.116499286574136</v>
       </c>
       <c r="U30" s="2" t="n">
-        <v>13.99363271250953</v>
+        <v>13.84425360706726</v>
       </c>
       <c r="V30" s="2" t="n">
-        <v>42.63122633153601</v>
+        <v>42.0872231650101</v>
       </c>
     </row>
     <row r="31">
@@ -8752,10 +8904,10 @@
         <v>5.92464919288274</v>
       </c>
       <c r="U31" s="2" t="n">
-        <v>8.607418744188681</v>
+        <v>8.765006713130532</v>
       </c>
       <c r="V31" s="2" t="n">
-        <v>20.73169030434976</v>
+        <v>20.71483929978241</v>
       </c>
     </row>
     <row r="32">
@@ -8822,10 +8974,10 @@
         <v>23.69453227715281</v>
       </c>
       <c r="U32" s="2" t="n">
-        <v>37.07991284551798</v>
+        <v>37.03301745534043</v>
       </c>
       <c r="V32" s="2" t="n">
-        <v>193.9657138026615</v>
+        <v>198.8920305098167</v>
       </c>
     </row>
     <row r="33">
@@ -8892,10 +9044,10 @@
         <v>4.346392164273192</v>
       </c>
       <c r="U33" s="2" t="n">
-        <v>6.440365384248689</v>
+        <v>6.495924005921536</v>
       </c>
       <c r="V33" s="2" t="n">
-        <v>15.62458079018737</v>
+        <v>15.8112164443005</v>
       </c>
     </row>
     <row r="34">
@@ -8962,10 +9114,10 @@
         <v>6.008062253548601</v>
       </c>
       <c r="U34" s="2" t="n">
-        <v>8.937116598589078</v>
+        <v>9.002898026402452</v>
       </c>
       <c r="V34" s="2" t="n">
-        <v>27.74284011001055</v>
+        <v>27.58750158265776</v>
       </c>
     </row>
     <row r="35">
@@ -9032,10 +9184,10 @@
         <v>9.620180946969663</v>
       </c>
       <c r="U35" s="2" t="n">
-        <v>18.32235754801641</v>
+        <v>17.9940861357088</v>
       </c>
       <c r="V35" s="2" t="n">
-        <v>242.6661867184066</v>
+        <v>246.8718593298187</v>
       </c>
     </row>
     <row r="36">
@@ -9102,10 +9254,10 @@
         <v>2.689677765222917</v>
       </c>
       <c r="U36" s="2" t="n">
-        <v>3.369022793512765</v>
+        <v>3.424639910789617</v>
       </c>
       <c r="V36" s="2" t="n">
-        <v>4.859103391713663</v>
+        <v>5.002266311184844</v>
       </c>
     </row>
     <row r="37">
@@ -9172,10 +9324,10 @@
         <v>19.73449331821678</v>
       </c>
       <c r="U37" s="2" t="n">
-        <v>34.44980522366983</v>
+        <v>35.38715972731723</v>
       </c>
       <c r="V37" s="2" t="n">
-        <v>422.815950852263</v>
+        <v>427.7277128735025</v>
       </c>
     </row>
     <row r="38">
@@ -9242,10 +9394,10 @@
         <v>4.812425993220381</v>
       </c>
       <c r="U38" s="2" t="n">
-        <v>5.960208386095646</v>
+        <v>6.106719253388373</v>
       </c>
       <c r="V38" s="2" t="n">
-        <v>19.74001119591217</v>
+        <v>20.2690018570508</v>
       </c>
     </row>
     <row r="39">
@@ -9666,10 +9818,10 @@
         <v>1.008629161958598</v>
       </c>
       <c r="U3" s="2" t="n">
-        <v>1.007752776423084</v>
+        <v>1.008016146229588</v>
       </c>
       <c r="V3" s="2" t="n">
-        <v>0.995222499887902</v>
+        <v>0.9952224998879019</v>
       </c>
     </row>
     <row r="4">
@@ -9736,10 +9888,10 @@
         <v>304.3332323568129</v>
       </c>
       <c r="U4" s="2" t="n">
-        <v>752.5624523165404</v>
+        <v>742.1649659561815</v>
       </c>
       <c r="V4" s="2" t="n">
-        <v>20802.4326168081</v>
+        <v>21695.25266434331</v>
       </c>
     </row>
     <row r="5">
@@ -9806,10 +9958,10 @@
         <v>1492.975981078933</v>
       </c>
       <c r="U5" s="2" t="n">
-        <v>3498.089216485562</v>
+        <v>3469.628719321709</v>
       </c>
       <c r="V5" s="2" t="n">
-        <v>851200.3935775722</v>
+        <v>879139.5075075517</v>
       </c>
     </row>
     <row r="6">
@@ -9876,10 +10028,10 @@
         <v>5428.429196523921</v>
       </c>
       <c r="U6" s="2" t="n">
-        <v>13491.47359542066</v>
+        <v>13423.92335965779</v>
       </c>
       <c r="V6" s="2" t="n">
-        <v>365406.3095555897</v>
+        <v>368249.9207858762</v>
       </c>
     </row>
     <row r="7">
@@ -9946,10 +10098,10 @@
         <v>9568.831724452888</v>
       </c>
       <c r="U7" s="2" t="n">
-        <v>22080.98332526741</v>
+        <v>21735.71582340555</v>
       </c>
       <c r="V7" s="2" t="n">
-        <v>3981241.544519183</v>
+        <v>4104229.031155468</v>
       </c>
     </row>
     <row r="8">
@@ -10016,10 +10168,10 @@
         <v>82.32322944213459</v>
       </c>
       <c r="U8" s="2" t="n">
-        <v>194.2386505453485</v>
+        <v>196.7045734834864</v>
       </c>
       <c r="V8" s="2" t="n">
-        <v>4686.07721294298</v>
+        <v>4875.473380713382</v>
       </c>
     </row>
     <row r="9">
@@ -10086,10 +10238,10 @@
         <v>50.00067972328989</v>
       </c>
       <c r="U9" s="2" t="n">
-        <v>115.2884559238654</v>
+        <v>116.3771315428858</v>
       </c>
       <c r="V9" s="2" t="n">
-        <v>756.4086308488268</v>
+        <v>773.5898693229019</v>
       </c>
     </row>
     <row r="10">
@@ -10156,10 +10308,10 @@
         <v>32.18844881440729</v>
       </c>
       <c r="U10" s="2" t="n">
-        <v>63.33657414094962</v>
+        <v>61.38323918231102</v>
       </c>
       <c r="V10" s="2" t="n">
-        <v>443.4751538077708</v>
+        <v>436.0900935006518</v>
       </c>
     </row>
     <row r="11">
@@ -10226,10 +10378,10 @@
         <v>17.21811430080176</v>
       </c>
       <c r="U11" s="2" t="n">
-        <v>30.70793432881509</v>
+        <v>31.37764895818272</v>
       </c>
       <c r="V11" s="2" t="n">
-        <v>243.6943185809622</v>
+        <v>250.6349616303636</v>
       </c>
     </row>
     <row r="12">
@@ -10296,10 +10448,10 @@
         <v>12.62464148874943</v>
       </c>
       <c r="U12" s="2" t="n">
-        <v>19.56725046656314</v>
+        <v>19.62196367199751</v>
       </c>
       <c r="V12" s="2" t="n">
-        <v>84.14671703747628</v>
+        <v>85.28246102658841</v>
       </c>
     </row>
     <row r="13">
@@ -10366,10 +10518,10 @@
         <v>44.47333251218827</v>
       </c>
       <c r="U13" s="2" t="n">
-        <v>76.02720668617863</v>
+        <v>77.49397502374835</v>
       </c>
       <c r="V13" s="2" t="n">
-        <v>398.5060770083255</v>
+        <v>406.0871436305475</v>
       </c>
     </row>
     <row r="14">
@@ -10436,10 +10588,10 @@
         <v>18.05777036079494</v>
       </c>
       <c r="U14" s="2" t="n">
-        <v>31.2819986133635</v>
+        <v>31.54192802989084</v>
       </c>
       <c r="V14" s="2" t="n">
-        <v>264.4713644926504</v>
+        <v>269.9119415904116</v>
       </c>
     </row>
     <row r="15">
@@ -10506,10 +10658,10 @@
         <v>26.00586422754296</v>
       </c>
       <c r="U15" s="2" t="n">
-        <v>58.24381920311886</v>
+        <v>58.59712637972502</v>
       </c>
       <c r="V15" s="2" t="n">
-        <v>433.0802015836003</v>
+        <v>444.5706447547481</v>
       </c>
     </row>
     <row r="16">
@@ -10576,10 +10728,10 @@
         <v>21.72005085282455</v>
       </c>
       <c r="U16" s="2" t="n">
-        <v>39.78267862258517</v>
+        <v>39.33017180038939</v>
       </c>
       <c r="V16" s="2" t="n">
-        <v>246.2104582914199</v>
+        <v>249.53562033654</v>
       </c>
     </row>
     <row r="17">
@@ -10646,10 +10798,10 @@
         <v>22.82774046680624</v>
       </c>
       <c r="U17" s="2" t="n">
-        <v>42.51121833485472</v>
+        <v>42.76342839301487</v>
       </c>
       <c r="V17" s="2" t="n">
-        <v>193.8368982482251</v>
+        <v>199.476508548944</v>
       </c>
     </row>
     <row r="18">
@@ -10716,10 +10868,10 @@
         <v>42.9922604911004</v>
       </c>
       <c r="U18" s="2" t="n">
-        <v>92.53618333706638</v>
+        <v>93.04425288505252</v>
       </c>
       <c r="V18" s="2" t="n">
-        <v>984.3859855664418</v>
+        <v>997.5740475825862</v>
       </c>
     </row>
     <row r="19">
@@ -10786,10 +10938,10 @@
         <v>29.8238831557871</v>
       </c>
       <c r="U19" s="2" t="n">
-        <v>61.15545970131198</v>
+        <v>62.27657087196675</v>
       </c>
       <c r="V19" s="2" t="n">
-        <v>591.37642032851</v>
+        <v>594.4319588755127</v>
       </c>
     </row>
     <row r="20">
@@ -10856,10 +11008,10 @@
         <v>24.05207048768307</v>
       </c>
       <c r="U20" s="2" t="n">
-        <v>49.84573562743678</v>
+        <v>49.22277453393004</v>
       </c>
       <c r="V20" s="2" t="n">
-        <v>273.6884737488751</v>
+        <v>276.4589585725923</v>
       </c>
     </row>
     <row r="21">
@@ -10926,10 +11078,10 @@
         <v>43.9071954720966</v>
       </c>
       <c r="U21" s="2" t="n">
-        <v>104.3874999205393</v>
+        <v>102.3702816000078</v>
       </c>
       <c r="V21" s="2" t="n">
-        <v>624.1816559668533</v>
+        <v>627.3528167669332</v>
       </c>
     </row>
     <row r="22">
@@ -10996,10 +11148,10 @@
         <v>72.17779039044444</v>
       </c>
       <c r="U22" s="2" t="n">
-        <v>163.7954589295572</v>
+        <v>164.3907432483787</v>
       </c>
       <c r="V22" s="2" t="n">
-        <v>772.1359861133358</v>
+        <v>802.6979220092956</v>
       </c>
     </row>
     <row r="23">
@@ -11066,10 +11218,10 @@
         <v>51.42698729019422</v>
       </c>
       <c r="U23" s="2" t="n">
-        <v>107.8785886623308</v>
+        <v>110.8757957759221</v>
       </c>
       <c r="V23" s="2" t="n">
-        <v>1210.563065296902</v>
+        <v>1226.777069878792</v>
       </c>
     </row>
     <row r="24">
@@ -11136,10 +11288,10 @@
         <v>59.46878459014955</v>
       </c>
       <c r="U24" s="2" t="n">
-        <v>139.4752327032504</v>
+        <v>141.2973145864974</v>
       </c>
       <c r="V24" s="2" t="n">
-        <v>1932.647762735833</v>
+        <v>1969.265633804265</v>
       </c>
     </row>
     <row r="25">
@@ -11206,10 +11358,10 @@
         <v>70.93288291178348</v>
       </c>
       <c r="U25" s="2" t="n">
-        <v>170.3225231059668</v>
+        <v>171.2799446802703</v>
       </c>
       <c r="V25" s="2" t="n">
-        <v>1792.439430629529</v>
+        <v>1880.403394533115</v>
       </c>
     </row>
     <row r="26">
@@ -11276,10 +11428,10 @@
         <v>42.72445537308758</v>
       </c>
       <c r="U26" s="2" t="n">
-        <v>96.67541833104535</v>
+        <v>100.0490874662719</v>
       </c>
       <c r="V26" s="2" t="n">
-        <v>967.9914262949476</v>
+        <v>994.6946215783587</v>
       </c>
     </row>
     <row r="27">
@@ -11346,10 +11498,10 @@
         <v>31.5801549832506</v>
       </c>
       <c r="U27" s="2" t="n">
-        <v>72.52531821610054</v>
+        <v>70.66568663288975</v>
       </c>
       <c r="V27" s="2" t="n">
-        <v>593.6721562571793</v>
+        <v>610.0540138948419</v>
       </c>
     </row>
     <row r="28">
@@ -11416,10 +11568,10 @@
         <v>26.38915679194307</v>
       </c>
       <c r="U28" s="2" t="n">
-        <v>53.46667087865562</v>
+        <v>54.74518716987259</v>
       </c>
       <c r="V28" s="2" t="n">
-        <v>268.2617879872659</v>
+        <v>271.3129782298061</v>
       </c>
     </row>
     <row r="29">
@@ -11486,10 +11638,10 @@
         <v>16.10003412407702</v>
       </c>
       <c r="U29" s="2" t="n">
-        <v>31.69560108931946</v>
+        <v>32.32843994658725</v>
       </c>
       <c r="V29" s="2" t="n">
-        <v>564.2980549967825</v>
+        <v>587.9816292505517</v>
       </c>
     </row>
     <row r="30">
@@ -11556,10 +11708,10 @@
         <v>8.116499286574136</v>
       </c>
       <c r="U30" s="2" t="n">
-        <v>13.99363271250953</v>
+        <v>13.84425360706726</v>
       </c>
       <c r="V30" s="2" t="n">
-        <v>42.63122633153601</v>
+        <v>42.0872231650101</v>
       </c>
     </row>
     <row r="31">
@@ -11626,10 +11778,10 @@
         <v>5.92464919288274</v>
       </c>
       <c r="U31" s="2" t="n">
-        <v>8.607418744188681</v>
+        <v>8.765006713130532</v>
       </c>
       <c r="V31" s="2" t="n">
-        <v>20.73169030434976</v>
+        <v>20.71483929978241</v>
       </c>
     </row>
     <row r="32">
@@ -11696,10 +11848,10 @@
         <v>23.69453227715281</v>
       </c>
       <c r="U32" s="2" t="n">
-        <v>37.07991284551798</v>
+        <v>37.03301745534043</v>
       </c>
       <c r="V32" s="2" t="n">
-        <v>193.9657138026615</v>
+        <v>198.8920305098167</v>
       </c>
     </row>
     <row r="33">
@@ -11766,10 +11918,10 @@
         <v>4.346392164273192</v>
       </c>
       <c r="U33" s="2" t="n">
-        <v>6.440365384248689</v>
+        <v>6.495924005921536</v>
       </c>
       <c r="V33" s="2" t="n">
-        <v>15.62458079018737</v>
+        <v>15.8112164443005</v>
       </c>
     </row>
     <row r="34">
@@ -11836,10 +11988,10 @@
         <v>6.008062253548601</v>
       </c>
       <c r="U34" s="2" t="n">
-        <v>8.937116598589078</v>
+        <v>9.002898026402452</v>
       </c>
       <c r="V34" s="2" t="n">
-        <v>27.74284011001055</v>
+        <v>27.58750158265776</v>
       </c>
     </row>
     <row r="35">
@@ -11906,10 +12058,10 @@
         <v>9.620180946969663</v>
       </c>
       <c r="U35" s="2" t="n">
-        <v>18.32235754801641</v>
+        <v>17.9940861357088</v>
       </c>
       <c r="V35" s="2" t="n">
-        <v>242.6661867184066</v>
+        <v>246.8718593298187</v>
       </c>
     </row>
     <row r="36">
@@ -11976,10 +12128,10 @@
         <v>2.689677765222917</v>
       </c>
       <c r="U36" s="2" t="n">
-        <v>3.369022793512765</v>
+        <v>3.424639910789617</v>
       </c>
       <c r="V36" s="2" t="n">
-        <v>4.859103391713663</v>
+        <v>5.002266311184844</v>
       </c>
     </row>
     <row r="37">
@@ -12046,10 +12198,10 @@
         <v>19.73449331821678</v>
       </c>
       <c r="U37" s="2" t="n">
-        <v>34.44980522366983</v>
+        <v>35.38715972731723</v>
       </c>
       <c r="V37" s="2" t="n">
-        <v>422.815950852263</v>
+        <v>427.7277128735025</v>
       </c>
     </row>
     <row r="38">
@@ -12116,10 +12268,10 @@
         <v>4.812425993220381</v>
       </c>
       <c r="U38" s="2" t="n">
-        <v>5.960208386095646</v>
+        <v>6.106719253388373</v>
       </c>
       <c r="V38" s="2" t="n">
-        <v>19.74001119591217</v>
+        <v>20.2690018570508</v>
       </c>
     </row>
     <row r="39">
@@ -13711,22 +13863,22 @@
         </is>
       </c>
       <c r="B20" s="2" t="n">
-        <v>235.5168111784253</v>
+        <v>237.8121143869398</v>
       </c>
       <c r="C20" s="2" t="n">
-        <v>235.5168111784253</v>
+        <v>237.8121143869398</v>
       </c>
       <c r="D20" s="2" t="n">
-        <v>138.0666744096916</v>
+        <v>139.5491234385203</v>
       </c>
       <c r="E20" s="2" t="n">
         <v>130373.17</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>0.001806482201655642</v>
+        <v>0.001824087842513454</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>0.001059011408633322</v>
+        <v>0.001070382222343142</v>
       </c>
     </row>
     <row r="21">
@@ -13736,22 +13888,22 @@
         </is>
       </c>
       <c r="B21" s="2" t="n">
-        <v>1676.645174033029</v>
+        <v>1709.964581931913</v>
       </c>
       <c r="C21" s="2" t="n">
-        <v>1676.645174033029</v>
+        <v>1709.964581931913</v>
       </c>
       <c r="D21" s="2" t="n">
-        <v>1107.491036409682</v>
+        <v>1130.593927859901</v>
       </c>
       <c r="E21" s="2" t="n">
         <v>130373.17</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>0.01286035442747176</v>
+        <v>0.01311592394303148</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>0.008494777233764296</v>
+        <v>0.008671983107106327</v>
       </c>
     </row>
   </sheetData>
@@ -13827,10 +13979,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="C2" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -13855,10 +14007,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="C3" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -14054,7 +14206,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Christensen &amp; Pauly (1995): per-group TE^(1-TL) with global_TE=0.1.</t>
+          <t>Pauly &amp; Christensen (1995): per-group TE^(1-TL) with global_TE=0.1.</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -14071,7 +14223,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Christensen &amp; Pauly (1995): per-group TE^(1-TL) with global_TE='mean'.</t>
+          <t>Pauly &amp; Christensen (1995): per-group TE^(1-TL) with global_TE='mean'.</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">

--- a/PPREstimation/output/top10/36_1_South_China_Sea_SCS-2007_Northern_South_China_Sea_(2000s).xlsx
+++ b/PPREstimation/output/top10/36_1_South_China_Sea_SCS-2007_Northern_South_China_Sea_(2000s).xlsx
@@ -617,7 +617,6 @@
           <t>Import</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr"/>
       <c r="F2" s="2" t="n">
         <v>1</v>
       </c>
@@ -640,10 +639,10 @@
         <v>0</v>
       </c>
       <c r="M2" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O2" s="2" t="n">
         <v>0</v>
@@ -4037,7 +4036,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V40"/>
+  <dimension ref="A1:X40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -4175,6 +4174,16 @@
           <t>MC_new_TE_EEfix</t>
         </is>
       </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>SPPR_1995_TEmean_catch</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>Ulanowicz_globalTEmean_catch</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
@@ -4185,9 +4194,6 @@
           <t>diet_import</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
       <c r="F2" s="2" t="n">
         <v>0</v>
       </c>
@@ -4218,19 +4224,19 @@
       <c r="O2" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="P2" t="inlineStr"/>
       <c r="Q2" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="R2" t="inlineStr"/>
       <c r="S2" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="T2" t="inlineStr"/>
       <c r="U2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="V2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4243,9 +4249,6 @@
           <t>Detritus</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
       <c r="F3" s="2" t="n">
         <v>0</v>
       </c>
@@ -4295,6 +4298,9 @@
         <v>0</v>
       </c>
       <c r="V3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4307,11 +4313,8 @@
           <t>Marine turtles</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
       <c r="F4" s="2" t="n">
-        <v>79.13077093785046</v>
+        <v>12319.04869152304</v>
       </c>
       <c r="G4" s="2" t="n">
         <v>8531.368875234397</v>
@@ -4360,6 +4363,9 @@
       </c>
       <c r="V4" s="2" t="n">
         <v>14268.62512307632</v>
+      </c>
+      <c r="X4" t="n">
+        <v>78.91245788453989</v>
       </c>
     </row>
     <row r="5">
@@ -4371,11 +4377,8 @@
           <t>Other mammals</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
       <c r="F5" s="2" t="n">
-        <v>142.1874696828596</v>
+        <v>11607.42410828205</v>
       </c>
       <c r="G5" s="2" t="n">
         <v>358964.9088147706</v>
@@ -4424,6 +4427,9 @@
       </c>
       <c r="V5" s="2" t="n">
         <v>592776.6105618178</v>
+      </c>
+      <c r="X5" t="n">
+        <v>141.828447465895</v>
       </c>
     </row>
     <row r="6">
@@ -4435,11 +4441,8 @@
           <t>Pinnipeds</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
       <c r="F6" s="2" t="n">
-        <v>160.0481076813766</v>
+        <v>14938.53286454283</v>
       </c>
       <c r="G6" s="2" t="n">
         <v>143855.1808771674</v>
@@ -4488,6 +4491,9 @@
       </c>
       <c r="V6" s="2" t="n">
         <v>239328.6672069039</v>
+      </c>
+      <c r="X6" t="n">
+        <v>159.6173766459243</v>
       </c>
     </row>
     <row r="7">
@@ -4499,11 +4505,8 @@
           <t>Seabirds</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
       <c r="F7" s="2" t="n">
-        <v>81.59267023728844</v>
+        <v>6143.823519544978</v>
       </c>
       <c r="G7" s="2" t="n">
         <v>1749306.689417539</v>
@@ -4552,6 +4555,9 @@
       </c>
       <c r="V7" s="2" t="n">
         <v>2710824.468534396</v>
+      </c>
+      <c r="X7" t="n">
+        <v>81.3837422592906</v>
       </c>
     </row>
     <row r="8">
@@ -4563,11 +4569,8 @@
           <t>Pelagic sharks and rays</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
       <c r="F8" s="2" t="n">
-        <v>142.4694828582344</v>
+        <v>8083.989427267226</v>
       </c>
       <c r="G8" s="2" t="n">
         <v>1872.114518584991</v>
@@ -4616,6 +4619,9 @@
       </c>
       <c r="V8" s="2" t="n">
         <v>3261.887236450888</v>
+      </c>
+      <c r="X8" t="n">
+        <v>142.1219815451821</v>
       </c>
     </row>
     <row r="9">
@@ -4627,11 +4633,8 @@
           <t>Demersal sharks and rays</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
       <c r="F9" s="2" t="n">
-        <v>68.58818003620004</v>
+        <v>8056.248314564314</v>
       </c>
       <c r="G9" s="2" t="n">
         <v>297.717267228758</v>
@@ -4680,6 +4683,9 @@
       </c>
       <c r="V9" s="2" t="n">
         <v>481.4152786051081</v>
+      </c>
+      <c r="X9" t="n">
+        <v>68.40552485412681</v>
       </c>
     </row>
     <row r="10">
@@ -4691,11 +4697,8 @@
           <t>Pelagic fish (&gt; 30 cm)</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
       <c r="F10" s="2" t="n">
-        <v>55.85640038794747</v>
+        <v>1872.074522739652</v>
       </c>
       <c r="G10" s="2" t="n">
         <v>246.769374275144</v>
@@ -4744,6 +4747,9 @@
       </c>
       <c r="V10" s="2" t="n">
         <v>297.2156696521085</v>
+      </c>
+      <c r="X10" t="n">
+        <v>55.74331104113519</v>
       </c>
     </row>
     <row r="11">
@@ -4755,11 +4761,8 @@
           <t>Juvenile large pelagic fish</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
       <c r="F11" s="2" t="n">
-        <v>25.82706859699662</v>
+        <v>570.1130857960235</v>
       </c>
       <c r="G11" s="2" t="n">
         <v>141.1097147954934</v>
@@ -4808,6 +4811,9 @@
       </c>
       <c r="V11" s="2" t="n">
         <v>170.3826290998149</v>
+      </c>
+      <c r="X11" t="n">
+        <v>25.78123231558675</v>
       </c>
     </row>
     <row r="12">
@@ -4819,11 +4825,8 @@
           <t>Pelagic fish (≤ 30 cm)</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr"/>
       <c r="F12" s="2" t="n">
-        <v>16.59452018894429</v>
+        <v>124.7243576364892</v>
       </c>
       <c r="G12" s="2" t="n">
         <v>57.92859266673526</v>
@@ -4872,6 +4875,9 @@
       </c>
       <c r="V12" s="2" t="n">
         <v>59.62843795395747</v>
+      </c>
+      <c r="X12" t="n">
+        <v>16.5725138683968</v>
       </c>
     </row>
     <row r="13">
@@ -4883,11 +4889,8 @@
           <t>Melon seed</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr"/>
       <c r="F13" s="2" t="n">
-        <v>25.51594115328954</v>
+        <v>572.0098005797831</v>
       </c>
       <c r="G13" s="2" t="n">
         <v>207.9254851387398</v>
@@ -4936,6 +4939,9 @@
       </c>
       <c r="V13" s="2" t="n">
         <v>277.6455928826152</v>
+      </c>
+      <c r="X13" t="n">
+        <v>25.47276148345648</v>
       </c>
     </row>
     <row r="14">
@@ -4947,11 +4953,8 @@
           <t>Benthopelagic fish</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr"/>
       <c r="F14" s="2" t="n">
-        <v>20.32681469440346</v>
+        <v>296.5218796393104</v>
       </c>
       <c r="G14" s="2" t="n">
         <v>132.5021427727404</v>
@@ -5000,6 +5003,9 @@
       </c>
       <c r="V14" s="2" t="n">
         <v>182.4550943026635</v>
+      </c>
+      <c r="X14" t="n">
+        <v>20.29401586903074</v>
       </c>
     </row>
     <row r="15">
@@ -5011,11 +5017,8 @@
           <t>Adult demersal fish (&gt; 30 cm)</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr"/>
       <c r="F15" s="2" t="n">
-        <v>54.68733942214475</v>
+        <v>5995.318663063536</v>
       </c>
       <c r="G15" s="2" t="n">
         <v>172.9326181900025</v>
@@ -5064,6 +5067,9 @@
       </c>
       <c r="V15" s="2" t="n">
         <v>274.6700836649002</v>
+      </c>
+      <c r="X15" t="n">
+        <v>54.54501908534514</v>
       </c>
     </row>
     <row r="16">
@@ -5075,11 +5081,8 @@
           <t>Juvenile demersal fish (&gt; 30 cm)</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
       <c r="F16" s="2" t="n">
-        <v>21.76827284677207</v>
+        <v>568.6507741883261</v>
       </c>
       <c r="G16" s="2" t="n">
         <v>121.3807423299588</v>
@@ -5128,6 +5131,9 @@
       </c>
       <c r="V16" s="2" t="n">
         <v>157.9956322191315</v>
+      </c>
+      <c r="X16" t="n">
+        <v>21.72844629174261</v>
       </c>
     </row>
     <row r="17">
@@ -5139,11 +5145,8 @@
           <t>Demesral fish (≤ 30 cm)</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr"/>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr"/>
       <c r="F17" s="2" t="n">
-        <v>18.58499961540817</v>
+        <v>509.488703533082</v>
       </c>
       <c r="G17" s="2" t="n">
         <v>77.84548668662224</v>
@@ -5192,6 +5195,9 @@
       </c>
       <c r="V17" s="2" t="n">
         <v>123.5309737289706</v>
+      </c>
+      <c r="X17" t="n">
+        <v>18.55027753759551</v>
       </c>
     </row>
     <row r="18">
@@ -5203,11 +5209,8 @@
           <t>Croakers (&gt; 30 cm)</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr"/>
       <c r="F18" s="2" t="n">
-        <v>63.8142658541919</v>
+        <v>3459.651216111189</v>
       </c>
       <c r="G18" s="2" t="n">
         <v>409.7088020992239</v>
@@ -5256,6 +5259,9 @@
       </c>
       <c r="V18" s="2" t="n">
         <v>656.1652444063013</v>
+      </c>
+      <c r="X18" t="n">
+        <v>63.6663196568172</v>
       </c>
     </row>
     <row r="19">
@@ -5267,11 +5273,8 @@
           <t>Juvenile large croakers</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr"/>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr"/>
       <c r="F19" s="2" t="n">
-        <v>36.18714655878334</v>
+        <v>2127.69273499347</v>
       </c>
       <c r="G19" s="2" t="n">
         <v>262.4035312589724</v>
@@ -5320,6 +5323,9 @@
       </c>
       <c r="V19" s="2" t="n">
         <v>375.6377875876929</v>
+      </c>
+      <c r="X19" t="n">
+        <v>36.10515271356682</v>
       </c>
     </row>
     <row r="20">
@@ -5331,11 +5337,8 @@
           <t>Croakers (≤ 30 cm)</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr"/>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr"/>
       <c r="F20" s="2" t="n">
-        <v>41.12846034238603</v>
+        <v>1620.350335427757</v>
       </c>
       <c r="G20" s="2" t="n">
         <v>129.5625599175519</v>
@@ -5384,6 +5387,9 @@
       </c>
       <c r="V20" s="2" t="n">
         <v>177.9954044605451</v>
+      </c>
+      <c r="X20" t="n">
+        <v>41.04097859449921</v>
       </c>
     </row>
     <row r="21">
@@ -5395,11 +5401,8 @@
           <t>Adult groupers</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr"/>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr"/>
       <c r="F21" s="2" t="n">
-        <v>80.74951561132005</v>
+        <v>6396.219226681</v>
       </c>
       <c r="G21" s="2" t="n">
         <v>239.2999781652991</v>
@@ -5448,6 +5451,9 @@
       </c>
       <c r="V21" s="2" t="n">
         <v>393.8993581467373</v>
+      </c>
+      <c r="X21" t="n">
+        <v>80.54376538243071</v>
       </c>
     </row>
     <row r="22">
@@ -5459,11 +5465,8 @@
           <t>Snappers</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr"/>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr"/>
       <c r="F22" s="2" t="n">
-        <v>75.9521456733591</v>
+        <v>5571.719880673496</v>
       </c>
       <c r="G22" s="2" t="n">
         <v>312.8905595277827</v>
@@ -5512,6 +5515,9 @@
       </c>
       <c r="V22" s="2" t="n">
         <v>493.283286347489</v>
+      </c>
+      <c r="X22" t="n">
+        <v>75.76152708011951</v>
       </c>
     </row>
     <row r="23">
@@ -5523,11 +5529,8 @@
           <t>Pomfret (stromateids)</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr"/>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr"/>
       <c r="F23" s="2" t="n">
-        <v>65.06940969218766</v>
+        <v>1511.418791385453</v>
       </c>
       <c r="G23" s="2" t="n">
         <v>323.3011364087398</v>
@@ -5576,6 +5579,9 @@
       </c>
       <c r="V23" s="2" t="n">
         <v>855.8237626207754</v>
+      </c>
+      <c r="X23" t="n">
+        <v>64.93772900414858</v>
       </c>
     </row>
     <row r="24">
@@ -5587,11 +5593,8 @@
           <t>Adult hairtail (trichiurids)</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr"/>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr"/>
       <c r="F24" s="2" t="n">
-        <v>127.7306235992025</v>
+        <v>11661.02162829573</v>
       </c>
       <c r="G24" s="2" t="n">
         <v>781.9525975989801</v>
@@ -5640,6 +5643,9 @@
       </c>
       <c r="V24" s="2" t="n">
         <v>1295.392531013809</v>
+      </c>
+      <c r="X24" t="n">
+        <v>127.4049432002319</v>
       </c>
     </row>
     <row r="25">
@@ -5651,11 +5657,8 @@
           <t>Juvenile Hairtail (trichiurids)</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr"/>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr"/>
       <c r="F25" s="2" t="n">
-        <v>124.8124681309909</v>
+        <v>12015.63425340947</v>
       </c>
       <c r="G25" s="2" t="n">
         <v>689.9418223187871</v>
@@ -5704,6 +5707,9 @@
       </c>
       <c r="V25" s="2" t="n">
         <v>1224.427483263716</v>
+      </c>
+      <c r="X25" t="n">
+        <v>124.4815140319991</v>
       </c>
     </row>
     <row r="26">
@@ -5715,11 +5721,8 @@
           <t>Lizard fish (synodontids)</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr"/>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr"/>
       <c r="F26" s="2" t="n">
-        <v>98.22972147422452</v>
+        <v>7142.697665911311</v>
       </c>
       <c r="G26" s="2" t="n">
         <v>385.3255414423559</v>
@@ -5768,6 +5771,9 @@
       </c>
       <c r="V26" s="2" t="n">
         <v>644.6692788100942</v>
+      </c>
+      <c r="X26" t="n">
+        <v>97.99069360283772</v>
       </c>
     </row>
     <row r="27">
@@ -5779,11 +5785,8 @@
           <t>Bigeyes (priacanthids)</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr"/>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr"/>
       <c r="F27" s="2" t="n">
-        <v>55.7917773122886</v>
+        <v>4186.472602030585</v>
       </c>
       <c r="G27" s="2" t="n">
         <v>247.9267387836067</v>
@@ -5832,6 +5835,9 @@
       </c>
       <c r="V27" s="2" t="n">
         <v>377.6008816923421</v>
+      </c>
+      <c r="X27" t="n">
+        <v>55.65464995744869</v>
       </c>
     </row>
     <row r="28">
@@ -5843,11 +5849,8 @@
           <t>Threadfin bream (nemipterids)</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr"/>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr"/>
       <c r="F28" s="2" t="n">
-        <v>24.90605102771918</v>
+        <v>1174.577052411648</v>
       </c>
       <c r="G28" s="2" t="n">
         <v>114.5669309607025</v>
@@ -5896,6 +5899,9 @@
       </c>
       <c r="V28" s="2" t="n">
         <v>163.0380458625788</v>
+      </c>
+      <c r="X28" t="n">
+        <v>24.8516621226912</v>
       </c>
     </row>
     <row r="29">
@@ -5907,11 +5913,8 @@
           <t>Cephalopods</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr"/>
-      <c r="D29" t="inlineStr"/>
-      <c r="E29" t="inlineStr"/>
       <c r="F29" s="2" t="n">
-        <v>37.0163475376776</v>
+        <v>1015.167586331241</v>
       </c>
       <c r="G29" s="2" t="n">
         <v>192.4373284142812</v>
@@ -5960,6 +5963,9 @@
       </c>
       <c r="V29" s="2" t="n">
         <v>393.3544196533529</v>
+      </c>
+      <c r="X29" t="n">
+        <v>36.94334999121287</v>
       </c>
     </row>
     <row r="30">
@@ -5971,11 +5977,8 @@
           <t>Crabs</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr"/>
-      <c r="D30" t="inlineStr"/>
-      <c r="E30" t="inlineStr"/>
       <c r="F30" s="2" t="n">
-        <v>6.103340136739709</v>
+        <v>132.649168462151</v>
       </c>
       <c r="G30" s="2" t="n">
         <v>18.20774302512697</v>
@@ -6024,6 +6027,9 @@
       </c>
       <c r="V30" s="2" t="n">
         <v>21.98289703467697</v>
+      </c>
+      <c r="X30" t="n">
+        <v>6.09255978297989</v>
       </c>
     </row>
     <row r="31">
@@ -6035,11 +6041,8 @@
           <t>Shrimps</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr"/>
-      <c r="D31" t="inlineStr"/>
-      <c r="E31" t="inlineStr"/>
       <c r="F31" s="2" t="n">
-        <v>4.732719337904325</v>
+        <v>32.49844983573067</v>
       </c>
       <c r="G31" s="2" t="n">
         <v>11.22735560262887</v>
@@ -6088,6 +6091,9 @@
       </c>
       <c r="V31" s="2" t="n">
         <v>11.53011267098982</v>
+      </c>
+      <c r="X31" t="n">
+        <v>4.726799397607477</v>
       </c>
     </row>
     <row r="32">
@@ -6099,11 +6105,8 @@
           <t>Sessile/other invertebrates</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr"/>
-      <c r="D32" t="inlineStr"/>
-      <c r="E32" t="inlineStr"/>
       <c r="F32" s="2" t="n">
-        <v>12.16951318507242</v>
+        <v>93.96351581335125</v>
       </c>
       <c r="G32" s="2" t="n">
         <v>128.9002557544757</v>
@@ -6152,6 +6155,9 @@
       </c>
       <c r="V32" s="2" t="n">
         <v>135.0015100252899</v>
+      </c>
+      <c r="X32" t="n">
+        <v>12.15285112733697</v>
       </c>
     </row>
     <row r="33">
@@ -6163,11 +6169,8 @@
           <t>Non-ceph molluscs</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr"/>
-      <c r="D33" t="inlineStr"/>
-      <c r="E33" t="inlineStr"/>
       <c r="F33" s="2" t="n">
-        <v>2.858801229068266</v>
+        <v>25.19033236815324</v>
       </c>
       <c r="G33" s="2" t="n">
         <v>7.720126690094499</v>
@@ -6216,6 +6219,9 @@
       </c>
       <c r="V33" s="2" t="n">
         <v>8.332893762949299</v>
+      </c>
+      <c r="X33" t="n">
+        <v>2.855253181730931</v>
       </c>
     </row>
     <row r="34">
@@ -6227,11 +6233,8 @@
           <t>Benthic crustaceans</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr"/>
-      <c r="D34" t="inlineStr"/>
-      <c r="E34" t="inlineStr"/>
       <c r="F34" s="2" t="n">
-        <v>3.500320635281005</v>
+        <v>42.68378825852471</v>
       </c>
       <c r="G34" s="2" t="n">
         <v>12.76138145769689</v>
@@ -6280,6 +6283,9 @@
       </c>
       <c r="V34" s="2" t="n">
         <v>13.43459325370352</v>
+      </c>
+      <c r="X34" t="n">
+        <v>3.495613074676316</v>
       </c>
     </row>
     <row r="35">
@@ -6291,11 +6297,8 @@
           <t>Echinoderms</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr"/>
-      <c r="D35" t="inlineStr"/>
-      <c r="E35" t="inlineStr"/>
       <c r="F35" s="2" t="n">
-        <v>10.5280347045407</v>
+        <v>172.3607342563855</v>
       </c>
       <c r="G35" s="2" t="n">
         <v>93.79232650242868</v>
@@ -6344,6 +6347,9 @@
       </c>
       <c r="V35" s="2" t="n">
         <v>165.5161776883501</v>
+      </c>
+      <c r="X35" t="n">
+        <v>10.51067574864136</v>
       </c>
     </row>
     <row r="36">
@@ -6355,9 +6361,6 @@
           <t>Polychaetes</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr"/>
-      <c r="D36" t="inlineStr"/>
-      <c r="E36" t="inlineStr"/>
       <c r="F36" s="2" t="n">
         <v>0</v>
       </c>
@@ -6407,6 +6410,9 @@
         <v>0</v>
       </c>
       <c r="V36" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X36" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6419,11 +6425,8 @@
           <t>Jellyfish</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr"/>
-      <c r="D37" t="inlineStr"/>
-      <c r="E37" t="inlineStr"/>
       <c r="F37" s="2" t="n">
-        <v>19.951458973169</v>
+        <v>176.3906720129945</v>
       </c>
       <c r="G37" s="2" t="n">
         <v>103.489111054912</v>
@@ -6472,6 +6475,9 @@
       </c>
       <c r="V37" s="2" t="n">
         <v>299.6641780113497</v>
+      </c>
+      <c r="X37" t="n">
+        <v>19.92305448876702</v>
       </c>
     </row>
     <row r="38">
@@ -6483,11 +6489,8 @@
           <t>Zooplankton</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr"/>
-      <c r="D38" t="inlineStr"/>
-      <c r="E38" t="inlineStr"/>
       <c r="F38" s="2" t="n">
-        <v>3.767992221672503</v>
+        <v>10.47015290156945</v>
       </c>
       <c r="G38" s="2" t="n">
         <v>13.72549019607843</v>
@@ -6536,6 +6539,9 @@
       </c>
       <c r="V38" s="2" t="n">
         <v>14.20866587077268</v>
+      </c>
+      <c r="X38" t="n">
+        <v>3.765411838727136</v>
       </c>
     </row>
     <row r="39">
@@ -6547,9 +6553,6 @@
           <t>Benthic producer</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr"/>
-      <c r="D39" t="inlineStr"/>
-      <c r="E39" t="inlineStr"/>
       <c r="F39" s="2" t="n">
         <v>1</v>
       </c>
@@ -6601,6 +6604,9 @@
       <c r="V39" s="2" t="n">
         <v>1</v>
       </c>
+      <c r="X39" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
@@ -6611,9 +6617,6 @@
           <t>Phytoplankton</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr"/>
-      <c r="D40" t="inlineStr"/>
-      <c r="E40" t="inlineStr"/>
       <c r="F40" s="2" t="n">
         <v>1</v>
       </c>
@@ -6663,6 +6666,9 @@
         <v>1</v>
       </c>
       <c r="V40" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="X40" t="n">
         <v>1</v>
       </c>
     </row>
@@ -6677,7 +6683,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V40"/>
+  <dimension ref="A1:X40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -6815,6 +6821,16 @@
           <t>MC_new_TE_EEfix</t>
         </is>
       </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>SPPR_1995_TEmean_catch</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>Ulanowicz_globalTEmean_catch</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
@@ -6864,19 +6880,22 @@
       <c r="O2" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="P2" t="inlineStr"/>
       <c r="Q2" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="R2" t="inlineStr"/>
       <c r="S2" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="T2" t="inlineStr"/>
       <c r="U2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="V2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1</v>
+      </c>
+      <c r="X2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6949,6 +6968,12 @@
       <c r="V3" s="2" t="n">
         <v>0.9952224998879019</v>
       </c>
+      <c r="W3" t="n">
+        <v>1</v>
+      </c>
+      <c r="X3" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
@@ -6966,10 +6991,10 @@
         <v>92.24256345598573</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>27.31418978610884</v>
+        <v>203.4742262826109</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>151.0905713983999</v>
+        <v>24625.18054764025</v>
       </c>
       <c r="G4" s="2" t="n">
         <v>13160.04066290114</v>
@@ -7018,6 +7043,12 @@
       </c>
       <c r="V4" s="2" t="n">
         <v>21695.25266434331</v>
+      </c>
+      <c r="W4" t="n">
+        <v>27.27744748459443</v>
+      </c>
+      <c r="X4" t="n">
+        <v>150.6614603962932</v>
       </c>
     </row>
     <row r="5">
@@ -7036,10 +7067,10 @@
         <v>799.4419240463516</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>132.4255997701232</v>
+        <v>2572.489909339983</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>243.1121069760094</v>
+        <v>21780.53453107671</v>
       </c>
       <c r="G5" s="2" t="n">
         <v>536595.032745474</v>
@@ -7088,6 +7119,12 @@
       </c>
       <c r="V5" s="2" t="n">
         <v>879139.5075075517</v>
+      </c>
+      <c r="W5" t="n">
+        <v>132.1625255561036</v>
+      </c>
+      <c r="X5" t="n">
+        <v>242.4837565577851</v>
       </c>
     </row>
     <row r="6">
@@ -7106,10 +7143,10 @@
         <v>1296.59805999128</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>188.5810047274931</v>
+        <v>4540.408207496885</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>328.3540052642784</v>
+        <v>29857.10431356886</v>
       </c>
       <c r="G6" s="2" t="n">
         <v>225834.2834641851</v>
@@ -7158,6 +7195,12 @@
       </c>
       <c r="V6" s="2" t="n">
         <v>368249.9207858762</v>
+      </c>
+      <c r="W6" t="n">
+        <v>188.1792973049467</v>
+      </c>
+      <c r="X6" t="n">
+        <v>327.4714569120617</v>
       </c>
     </row>
     <row r="7">
@@ -7176,10 +7219,10 @@
         <v>251.2962624249528</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>56.82830306038112</v>
+        <v>660.4964974762869</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>157.6104131772235</v>
+        <v>11628.14467606138</v>
       </c>
       <c r="G7" s="2" t="n">
         <v>2677969.457824239</v>
@@ -7228,6 +7271,12 @@
       </c>
       <c r="V7" s="2" t="n">
         <v>4104229.031155468</v>
+      </c>
+      <c r="W7" t="n">
+        <v>56.7349399074545</v>
+      </c>
+      <c r="X7" t="n">
+        <v>157.2123070529474</v>
       </c>
     </row>
     <row r="8">
@@ -7246,10 +7295,10 @@
         <v>899.0500091778036</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>144.2950105717456</v>
+        <v>2953.028765671548</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>229.7486792198561</v>
+        <v>13809.9699312055</v>
       </c>
       <c r="G8" s="2" t="n">
         <v>2824.519338949478</v>
@@ -7298,6 +7347,12 @@
       </c>
       <c r="V8" s="2" t="n">
         <v>4875.473380713382</v>
+      </c>
+      <c r="W8" t="n">
+        <v>144.0033258928464</v>
+      </c>
+      <c r="X8" t="n">
+        <v>229.1792350985385</v>
       </c>
     </row>
     <row r="9">
@@ -7316,10 +7371,10 @@
         <v>308.1918315138685</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>65.97174957616915</v>
+        <v>839.4675277285165</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>160.7977841575243</v>
+        <v>16975.30394455348</v>
       </c>
       <c r="G9" s="2" t="n">
         <v>491.2861173340253</v>
@@ -7368,6 +7423,12 @@
       </c>
       <c r="V9" s="2" t="n">
         <v>773.5898693229019</v>
+      </c>
+      <c r="W9" t="n">
+        <v>65.85936559240864</v>
+      </c>
+      <c r="X9" t="n">
+        <v>160.3803233453069</v>
       </c>
     </row>
     <row r="10">
@@ -7386,10 +7447,10 @@
         <v>231.5583426224563</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>53.52972986556865</v>
+        <v>599.9749171465847</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>86.78574416591442</v>
+        <v>3244.534115816982</v>
       </c>
       <c r="G10" s="2" t="n">
         <v>361.8032428909736</v>
@@ -7438,6 +7499,12 @@
       </c>
       <c r="V10" s="2" t="n">
         <v>436.0900935006518</v>
+      </c>
+      <c r="W10" t="n">
+        <v>53.44308655505199</v>
+      </c>
+      <c r="X10" t="n">
+        <v>86.60650831361818</v>
       </c>
     </row>
     <row r="11">
@@ -7456,10 +7523,10 @@
         <v>76.4894348901223</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>23.81963953543361</v>
+        <v>163.2896108626231</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>41.1731402246601</v>
+        <v>961.311199535362</v>
       </c>
       <c r="G11" s="2" t="n">
         <v>207.6401444699276</v>
@@ -7508,6 +7575,12 @@
       </c>
       <c r="V11" s="2" t="n">
         <v>250.6349616303636</v>
+      </c>
+      <c r="W11" t="n">
+        <v>23.78892337363167</v>
+      </c>
+      <c r="X11" t="n">
+        <v>41.09899305506266</v>
       </c>
     </row>
     <row r="12">
@@ -7526,10 +7599,10 @@
         <v>60.47920317327088</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>20.06205118056265</v>
+        <v>123.916391975453</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>24.00573038479183</v>
+        <v>184.3334889019411</v>
       </c>
       <c r="G12" s="2" t="n">
         <v>82.96378175401139</v>
@@ -7578,6 +7651,12 @@
       </c>
       <c r="V12" s="2" t="n">
         <v>85.28246102658841</v>
+      </c>
+      <c r="W12" t="n">
+        <v>20.03758056299784</v>
+      </c>
+      <c r="X12" t="n">
+        <v>23.97346914860318</v>
       </c>
     </row>
     <row r="13">
@@ -7596,10 +7675,10 @@
         <v>99.1861239547322</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>28.80245418851694</v>
+        <v>221.5849768170285</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>39.30531307022012</v>
+        <v>947.0948277574396</v>
       </c>
       <c r="G13" s="2" t="n">
         <v>303.8057015764734</v>
@@ -7648,6 +7727,12 @@
       </c>
       <c r="V13" s="2" t="n">
         <v>406.0871436305475</v>
+      </c>
+      <c r="W13" t="n">
+        <v>28.76308884060976</v>
+      </c>
+      <c r="X13" t="n">
+        <v>39.23752949114421</v>
       </c>
     </row>
     <row r="14">
@@ -7666,10 +7751,10 @@
         <v>57.63885649831866</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>19.36885639926595</v>
+        <v>117.1076353098614</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>32.69415488144099</v>
+        <v>512.5799827947337</v>
       </c>
       <c r="G14" s="2" t="n">
         <v>196.0520754129374</v>
@@ -7718,6 +7803,12 @@
       </c>
       <c r="V14" s="2" t="n">
         <v>269.9119415904116</v>
+      </c>
+      <c r="W14" t="n">
+        <v>19.34550815905992</v>
+      </c>
+      <c r="X14" t="n">
+        <v>32.6398139702783</v>
       </c>
     </row>
     <row r="15">
@@ -7736,10 +7827,10 @@
         <v>258.3713541792175</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>57.99352042215541</v>
+        <v>682.3973168995113</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>133.3645545250341</v>
+        <v>12693.728405856</v>
       </c>
       <c r="G15" s="2" t="n">
         <v>289.5633692796501</v>
@@ -7788,6 +7879,12 @@
       </c>
       <c r="V15" s="2" t="n">
         <v>444.5706447547481</v>
+      </c>
+      <c r="W15" t="n">
+        <v>57.89776466431431</v>
+      </c>
+      <c r="X15" t="n">
+        <v>133.0290935791215</v>
       </c>
     </row>
     <row r="16">
@@ -7806,10 +7903,10 @@
         <v>107.184597272732</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>30.48253250849711</v>
+        <v>242.7231196463857</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>47.0259883288617</v>
+        <v>1189.135083047449</v>
       </c>
       <c r="G16" s="2" t="n">
         <v>195.3372270916634</v>
@@ -7858,6 +7955,12 @@
       </c>
       <c r="V16" s="2" t="n">
         <v>249.53562033654</v>
+      </c>
+      <c r="W16" t="n">
+        <v>30.44016856732753</v>
+      </c>
+      <c r="X16" t="n">
+        <v>46.93975457748277</v>
       </c>
     </row>
     <row r="17">
@@ -7876,10 +7979,10 @@
         <v>94.89020727664703</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>27.88511775272285</v>
+        <v>210.3528549204131</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>45.03806849341223</v>
+        <v>1121.780149892512</v>
       </c>
       <c r="G17" s="2" t="n">
         <v>129.3193046916342</v>
@@ -7928,6 +8031,12 @@
       </c>
       <c r="V17" s="2" t="n">
         <v>199.476508548944</v>
+      </c>
+      <c r="W17" t="n">
+        <v>27.8473729981765</v>
+      </c>
+      <c r="X17" t="n">
+        <v>44.95489195220384</v>
       </c>
     </row>
     <row r="18">
@@ -7946,10 +8055,10 @@
         <v>289.7876734589325</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>63.06811537136963</v>
+        <v>780.8845872970606</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>123.631482963851</v>
+        <v>6729.572839285409</v>
       </c>
       <c r="G18" s="2" t="n">
         <v>635.8737662720922</v>
@@ -7998,6 +8107,12 @@
       </c>
       <c r="V18" s="2" t="n">
         <v>997.5740475825862</v>
+      </c>
+      <c r="W18" t="n">
+        <v>62.96183117057813</v>
+      </c>
+      <c r="X18" t="n">
+        <v>123.3440906020121</v>
       </c>
     </row>
     <row r="19">
@@ -8016,10 +8131,10 @@
         <v>167.9268901447387</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>42.32427293966179</v>
+        <v>411.3330540590173</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>81.56408529214163</v>
+        <v>4421.558639851675</v>
       </c>
       <c r="G19" s="2" t="n">
         <v>424.4204120084829</v>
@@ -8068,6 +8183,12 @@
       </c>
       <c r="V19" s="2" t="n">
         <v>594.4319588755127</v>
+      </c>
+      <c r="W19" t="n">
+        <v>42.25980631304412</v>
+      </c>
+      <c r="X19" t="n">
+        <v>81.38230125747123</v>
       </c>
     </row>
     <row r="20">
@@ -8086,10 +8207,10 @@
         <v>201.3110327290003</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>48.32309556834325</v>
+        <v>508.9912364824458</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>84.45663634494716</v>
+        <v>3291.343690486387</v>
       </c>
       <c r="G20" s="2" t="n">
         <v>203.6989805411893</v>
@@ -8138,6 +8259,12 @@
       </c>
       <c r="V20" s="2" t="n">
         <v>276.4589585725923</v>
+      </c>
+      <c r="W20" t="n">
+        <v>48.24688898293754</v>
+      </c>
+      <c r="X20" t="n">
+        <v>84.27648247438202</v>
       </c>
     </row>
     <row r="21">
@@ -8156,10 +8283,10 @@
         <v>536.3996649668767</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>98.92105285427314</v>
+        <v>1609.730472625195</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>192.0354449831898</v>
+        <v>13598.16488141827</v>
       </c>
       <c r="G21" s="2" t="n">
         <v>393.6118730166681</v>
@@ -8208,6 +8335,12 @@
       </c>
       <c r="V21" s="2" t="n">
         <v>627.3528167669332</v>
+      </c>
+      <c r="W21" t="n">
+        <v>98.73625924615786</v>
+      </c>
+      <c r="X21" t="n">
+        <v>191.5559801475918</v>
       </c>
     </row>
     <row r="22">
@@ -8226,10 +8359,10 @@
         <v>536.6382306190739</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>98.95321215930086</v>
+        <v>1610.571623171643</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>189.1980214024598</v>
+        <v>12376.73357180041</v>
       </c>
       <c r="G22" s="2" t="n">
         <v>525.0908437910632</v>
@@ -8278,6 +8411,12 @@
       </c>
       <c r="V22" s="2" t="n">
         <v>802.6979220092956</v>
+      </c>
+      <c r="W22" t="n">
+        <v>98.76834540849386</v>
+      </c>
+      <c r="X22" t="n">
+        <v>188.7299541478544</v>
       </c>
     </row>
     <row r="23">
@@ -8296,10 +8435,10 @@
         <v>336.3938507057656</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>70.33251350885153</v>
+        <v>930.4221122812825</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>96.95685657472633</v>
+        <v>2272.634239207302</v>
       </c>
       <c r="G23" s="2" t="n">
         <v>465.6307424829084</v>
@@ -8348,6 +8487,12 @@
       </c>
       <c r="V23" s="2" t="n">
         <v>1226.777069878792</v>
+      </c>
+      <c r="W23" t="n">
+        <v>70.21087184652784</v>
+      </c>
+      <c r="X23" t="n">
+        <v>96.76069753557947</v>
       </c>
     </row>
     <row r="24">
@@ -8366,10 +8511,10 @@
         <v>770.807846749354</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>128.9413282955242</v>
+        <v>2464.580714764936</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>238.8642044033908</v>
+        <v>23107.00660545965</v>
       </c>
       <c r="G24" s="2" t="n">
         <v>1197.942600408966</v>
@@ -8418,6 +8563,12 @@
       </c>
       <c r="V24" s="2" t="n">
         <v>1969.265633804265</v>
+      </c>
+      <c r="W24" t="n">
+        <v>128.6865723369627</v>
+      </c>
+      <c r="X24" t="n">
+        <v>238.2414834870946</v>
       </c>
     </row>
     <row r="25">
@@ -8436,10 +8587,10 @@
         <v>694.8941689734651</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>119.5298923502131</v>
+        <v>2181.937520325551</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>253.1629649309714</v>
+        <v>24146.03069088473</v>
       </c>
       <c r="G25" s="2" t="n">
         <v>1076.336205971309</v>
@@ -8488,6 +8639,12 @@
       </c>
       <c r="V25" s="2" t="n">
         <v>1880.403394533115</v>
+      </c>
+      <c r="W25" t="n">
+        <v>119.2974108495846</v>
+      </c>
+      <c r="X25" t="n">
+        <v>252.4893979315975</v>
       </c>
     </row>
     <row r="26">
@@ -8506,10 +8663,10 @@
         <v>663.7195178466512</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>115.5857987991034</v>
+        <v>2067.391179715494</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>193.9820464701548</v>
+        <v>14570.76074672779</v>
       </c>
       <c r="G26" s="2" t="n">
         <v>601.5468445458777</v>
@@ -8558,6 +8715,12 @@
       </c>
       <c r="V26" s="2" t="n">
         <v>994.6946215783587</v>
+      </c>
+      <c r="W26" t="n">
+        <v>115.3625637881615</v>
+      </c>
+      <c r="X26" t="n">
+        <v>193.5009343942022</v>
       </c>
     </row>
     <row r="27">
@@ -8576,10 +8739,10 @@
         <v>283.3262427405791</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>62.03702685919393</v>
+        <v>760.4687493012735</v>
       </c>
       <c r="F27" s="2" t="n">
-        <v>133.9962329328119</v>
+        <v>9080.748733909966</v>
       </c>
       <c r="G27" s="2" t="n">
         <v>410.4710283049905</v>
@@ -8628,6 +8791,12 @@
       </c>
       <c r="V27" s="2" t="n">
         <v>610.0540138948419</v>
+      </c>
+      <c r="W27" t="n">
+        <v>61.93289577099692</v>
+      </c>
+      <c r="X27" t="n">
+        <v>133.6701614106587</v>
       </c>
     </row>
     <row r="28">
@@ -8646,10 +8815,10 @@
         <v>158.4407803789103</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>40.56290610566914</v>
+        <v>384.1710875357484</v>
       </c>
       <c r="F28" s="2" t="n">
-        <v>69.14309272006736</v>
+        <v>2655.762506698117</v>
       </c>
       <c r="G28" s="2" t="n">
         <v>197.3866593685044</v>
@@ -8698,6 +8867,12 @@
       </c>
       <c r="V28" s="2" t="n">
         <v>271.3129782298061</v>
+      </c>
+      <c r="W28" t="n">
+        <v>40.50182298858382</v>
+      </c>
+      <c r="X28" t="n">
+        <v>68.99987341672315</v>
       </c>
     </row>
     <row r="29">
@@ -8716,10 +8891,10 @@
         <v>165.1796771222783</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>41.81699351005042</v>
+        <v>403.4385375229931</v>
       </c>
       <c r="F29" s="2" t="n">
-        <v>65.6922890975089</v>
+        <v>1806.275122137974</v>
       </c>
       <c r="G29" s="2" t="n">
         <v>290.5457815524936</v>
@@ -8768,6 +8943,12 @@
       </c>
       <c r="V29" s="2" t="n">
         <v>587.9816292505517</v>
+      </c>
+      <c r="W29" t="n">
+        <v>41.75350445389972</v>
+      </c>
+      <c r="X29" t="n">
+        <v>65.56164845420059</v>
       </c>
     </row>
     <row r="30">
@@ -8786,10 +8967,10 @@
         <v>33.25478525090308</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>12.95667542933245</v>
+        <v>61.37025533713454</v>
       </c>
       <c r="F30" s="2" t="n">
-        <v>23.99611880245712</v>
+        <v>361.2652457354941</v>
       </c>
       <c r="G30" s="2" t="n">
         <v>36.39332338325889</v>
@@ -8838,6 +9019,12 @@
       </c>
       <c r="V30" s="2" t="n">
         <v>42.0872231650101</v>
+      </c>
+      <c r="W30" t="n">
+        <v>12.94317451570484</v>
+      </c>
+      <c r="X30" t="n">
+        <v>23.95793731437822</v>
       </c>
     </row>
     <row r="31">
@@ -8856,10 +9043,10 @@
         <v>20.60629913269998</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>9.131659564304259</v>
+        <v>34.97513898062208</v>
       </c>
       <c r="F31" s="2" t="n">
-        <v>12.79079223465034</v>
+        <v>80.50966404685303</v>
       </c>
       <c r="G31" s="2" t="n">
         <v>20.32061106033339</v>
@@ -8908,6 +9095,12 @@
       </c>
       <c r="V31" s="2" t="n">
         <v>20.71483929978241</v>
+      </c>
+      <c r="W31" t="n">
+        <v>9.123443335229625</v>
+      </c>
+      <c r="X31" t="n">
+        <v>12.77580658762833</v>
       </c>
     </row>
     <row r="32">
@@ -8926,10 +9119,10 @@
         <v>39.81071705534973</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>14.77811807337469</v>
+        <v>75.81724064970111</v>
       </c>
       <c r="F32" s="2" t="n">
-        <v>19.53815724820203</v>
+        <v>140.2165385342558</v>
       </c>
       <c r="G32" s="2" t="n">
         <v>190.4040920716112</v>
@@ -8978,6 +9171,12 @@
       </c>
       <c r="V32" s="2" t="n">
         <v>198.8920305098167</v>
+      </c>
+      <c r="W32" t="n">
+        <v>14.76192892366971</v>
+      </c>
+      <c r="X32" t="n">
+        <v>19.51287980403976</v>
       </c>
     </row>
     <row r="33">
@@ -8996,10 +9195,10 @@
         <v>14.71217112194568</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>7.138150161957237</v>
+        <v>23.54240736127333</v>
       </c>
       <c r="F33" s="2" t="n">
-        <v>9.86572583660954</v>
+        <v>66.94570262780725</v>
       </c>
       <c r="G33" s="2" t="n">
         <v>14.79760102200063</v>
@@ -9048,6 +9247,12 @@
       </c>
       <c r="V33" s="2" t="n">
         <v>15.8112164443005</v>
+      </c>
+      <c r="W33" t="n">
+        <v>7.132442509188241</v>
+      </c>
+      <c r="X33" t="n">
+        <v>9.85463556313668</v>
       </c>
     </row>
     <row r="34">
@@ -9066,10 +9271,10 @@
         <v>15.81299528405932</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>7.524777705808002</v>
+        <v>25.62522809850928</v>
       </c>
       <c r="F34" s="2" t="n">
-        <v>11.75404832527506</v>
+        <v>117.6611600421435</v>
       </c>
       <c r="G34" s="2" t="n">
         <v>26.52199690564272</v>
@@ -9118,6 +9323,12 @@
       </c>
       <c r="V34" s="2" t="n">
         <v>27.58750158265776</v>
+      </c>
+      <c r="W34" t="n">
+        <v>7.518599497541913</v>
+      </c>
+      <c r="X34" t="n">
+        <v>11.73902826550227</v>
       </c>
     </row>
     <row r="35">
@@ -9136,10 +9347,10 @@
         <v>18.61708723298873</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>8.478531976146394</v>
+        <v>31.04288882388031</v>
       </c>
       <c r="F35" s="2" t="n">
-        <v>18.48000840404622</v>
+        <v>287.9969723030186</v>
       </c>
       <c r="G35" s="2" t="n">
         <v>140.2531467766166</v>
@@ -9188,6 +9399,12 @@
       </c>
       <c r="V35" s="2" t="n">
         <v>246.8718593298187</v>
+      </c>
+      <c r="W35" t="n">
+        <v>8.471159248049466</v>
+      </c>
+      <c r="X35" t="n">
+        <v>18.44967698338515</v>
       </c>
     </row>
     <row r="36">
@@ -9206,10 +9423,10 @@
         <v>10</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>5.38284603096072</v>
+        <v>14.95736128795635</v>
       </c>
       <c r="F36" s="2" t="n">
-        <v>5.38284603096072</v>
+        <v>14.95736128795635</v>
       </c>
       <c r="G36" s="2" t="n">
         <v>4.952947003467063</v>
@@ -9258,6 +9475,12 @@
       </c>
       <c r="V36" s="2" t="n">
         <v>5.002266311184844</v>
+      </c>
+      <c r="W36" t="n">
+        <v>5.379159769610195</v>
+      </c>
+      <c r="X36" t="n">
+        <v>5.379159769610195</v>
       </c>
     </row>
     <row r="37">
@@ -9276,10 +9499,10 @@
         <v>103.7909360953989</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>29.77396345132429</v>
+        <v>233.7195026604724</v>
       </c>
       <c r="F37" s="2" t="n">
-        <v>28.53269211364632</v>
+        <v>253.7361002571505</v>
       </c>
       <c r="G37" s="2" t="n">
         <v>147.8720821296587</v>
@@ -9328,6 +9551,12 @@
       </c>
       <c r="V37" s="2" t="n">
         <v>427.7277128735025</v>
+      </c>
+      <c r="W37" t="n">
+        <v>29.73286887071495</v>
+      </c>
+      <c r="X37" t="n">
+        <v>28.49200913915451</v>
       </c>
     </row>
     <row r="38">
@@ -9346,10 +9575,10 @@
         <v>10</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>5.38284603096072</v>
+        <v>14.95736128795635</v>
       </c>
       <c r="F38" s="2" t="n">
-        <v>5.382846030960719</v>
+        <v>14.95736128795635</v>
       </c>
       <c r="G38" s="2" t="n">
         <v>19.6078431372549</v>
@@ -9398,6 +9627,12 @@
       </c>
       <c r="V38" s="2" t="n">
         <v>20.2690018570508</v>
+      </c>
+      <c r="W38" t="n">
+        <v>5.379159769610195</v>
+      </c>
+      <c r="X38" t="n">
+        <v>5.379159769610194</v>
       </c>
     </row>
     <row r="39">
@@ -9469,6 +9704,12 @@
       <c r="V39" s="2" t="n">
         <v>1</v>
       </c>
+      <c r="W39" t="n">
+        <v>1</v>
+      </c>
+      <c r="X39" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
@@ -9537,6 +9778,12 @@
         <v>1</v>
       </c>
       <c r="V40" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="W40" t="n">
+        <v>1</v>
+      </c>
+      <c r="X40" t="n">
         <v>1</v>
       </c>
     </row>
@@ -9551,7 +9798,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V40"/>
+  <dimension ref="A1:X40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -9689,6 +9936,16 @@
           <t>MC_new_TE_EEfix</t>
         </is>
       </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>SPPR_1995_TEmean_catch</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>Ulanowicz_globalTEmean_catch</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
@@ -9738,19 +9995,22 @@
       <c r="O2" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="P2" t="inlineStr"/>
       <c r="Q2" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="R2" t="inlineStr"/>
       <c r="S2" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="T2" t="inlineStr"/>
       <c r="U2" s="2" t="n">
         <v>1</v>
       </c>
       <c r="V2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1</v>
+      </c>
+      <c r="X2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -9823,6 +10083,12 @@
       <c r="V3" s="2" t="n">
         <v>0.9952224998879019</v>
       </c>
+      <c r="W3" t="n">
+        <v>1</v>
+      </c>
+      <c r="X3" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
@@ -9840,10 +10106,10 @@
         <v>92.24256345598573</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>27.31418978610884</v>
+        <v>203.4742262826109</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>151.0905713983999</v>
+        <v>24625.18054764025</v>
       </c>
       <c r="G4" s="2" t="n">
         <v>13160.04066290114</v>
@@ -9892,6 +10158,12 @@
       </c>
       <c r="V4" s="2" t="n">
         <v>21695.25266434331</v>
+      </c>
+      <c r="W4" t="n">
+        <v>27.27744748459443</v>
+      </c>
+      <c r="X4" t="n">
+        <v>150.6614603962932</v>
       </c>
     </row>
     <row r="5">
@@ -9910,10 +10182,10 @@
         <v>799.4419240463516</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>132.4255997701232</v>
+        <v>2572.489909339983</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>243.1121069760094</v>
+        <v>21780.53453107671</v>
       </c>
       <c r="G5" s="2" t="n">
         <v>536595.032745474</v>
@@ -9962,6 +10234,12 @@
       </c>
       <c r="V5" s="2" t="n">
         <v>879139.5075075517</v>
+      </c>
+      <c r="W5" t="n">
+        <v>132.1625255561036</v>
+      </c>
+      <c r="X5" t="n">
+        <v>242.4837565577851</v>
       </c>
     </row>
     <row r="6">
@@ -9980,10 +10258,10 @@
         <v>1296.59805999128</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>188.5810047274931</v>
+        <v>4540.408207496885</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>328.3540052642784</v>
+        <v>29857.10431356886</v>
       </c>
       <c r="G6" s="2" t="n">
         <v>225834.2834641851</v>
@@ -10032,6 +10310,12 @@
       </c>
       <c r="V6" s="2" t="n">
         <v>368249.9207858762</v>
+      </c>
+      <c r="W6" t="n">
+        <v>188.1792973049467</v>
+      </c>
+      <c r="X6" t="n">
+        <v>327.4714569120617</v>
       </c>
     </row>
     <row r="7">
@@ -10050,10 +10334,10 @@
         <v>251.2962624249528</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>56.82830306038112</v>
+        <v>660.4964974762869</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>157.6104131772235</v>
+        <v>11628.14467606138</v>
       </c>
       <c r="G7" s="2" t="n">
         <v>2677969.457824239</v>
@@ -10102,6 +10386,12 @@
       </c>
       <c r="V7" s="2" t="n">
         <v>4104229.031155468</v>
+      </c>
+      <c r="W7" t="n">
+        <v>56.7349399074545</v>
+      </c>
+      <c r="X7" t="n">
+        <v>157.2123070529474</v>
       </c>
     </row>
     <row r="8">
@@ -10120,10 +10410,10 @@
         <v>899.0500091778036</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>144.2950105717456</v>
+        <v>2953.028765671548</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>229.7486792198561</v>
+        <v>13809.9699312055</v>
       </c>
       <c r="G8" s="2" t="n">
         <v>2824.519338949478</v>
@@ -10172,6 +10462,12 @@
       </c>
       <c r="V8" s="2" t="n">
         <v>4875.473380713382</v>
+      </c>
+      <c r="W8" t="n">
+        <v>144.0033258928464</v>
+      </c>
+      <c r="X8" t="n">
+        <v>229.1792350985385</v>
       </c>
     </row>
     <row r="9">
@@ -10190,10 +10486,10 @@
         <v>308.1918315138685</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>65.97174957616915</v>
+        <v>839.4675277285165</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>160.7977841575243</v>
+        <v>16975.30394455348</v>
       </c>
       <c r="G9" s="2" t="n">
         <v>491.2861173340253</v>
@@ -10242,6 +10538,12 @@
       </c>
       <c r="V9" s="2" t="n">
         <v>773.5898693229019</v>
+      </c>
+      <c r="W9" t="n">
+        <v>65.85936559240864</v>
+      </c>
+      <c r="X9" t="n">
+        <v>160.3803233453069</v>
       </c>
     </row>
     <row r="10">
@@ -10260,10 +10562,10 @@
         <v>231.5583426224563</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>53.52972986556865</v>
+        <v>599.9749171465847</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>86.78574416591442</v>
+        <v>3244.534115816982</v>
       </c>
       <c r="G10" s="2" t="n">
         <v>361.8032428909736</v>
@@ -10312,6 +10614,12 @@
       </c>
       <c r="V10" s="2" t="n">
         <v>436.0900935006518</v>
+      </c>
+      <c r="W10" t="n">
+        <v>53.44308655505199</v>
+      </c>
+      <c r="X10" t="n">
+        <v>86.60650831361818</v>
       </c>
     </row>
     <row r="11">
@@ -10330,10 +10638,10 @@
         <v>76.4894348901223</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>23.81963953543361</v>
+        <v>163.2896108626231</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>41.1731402246601</v>
+        <v>961.311199535362</v>
       </c>
       <c r="G11" s="2" t="n">
         <v>207.6401444699276</v>
@@ -10382,6 +10690,12 @@
       </c>
       <c r="V11" s="2" t="n">
         <v>250.6349616303636</v>
+      </c>
+      <c r="W11" t="n">
+        <v>23.78892337363167</v>
+      </c>
+      <c r="X11" t="n">
+        <v>41.09899305506266</v>
       </c>
     </row>
     <row r="12">
@@ -10400,10 +10714,10 @@
         <v>60.47920317327088</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>20.06205118056265</v>
+        <v>123.916391975453</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>24.00573038479183</v>
+        <v>184.3334889019411</v>
       </c>
       <c r="G12" s="2" t="n">
         <v>82.96378175401139</v>
@@ -10452,6 +10766,12 @@
       </c>
       <c r="V12" s="2" t="n">
         <v>85.28246102658841</v>
+      </c>
+      <c r="W12" t="n">
+        <v>20.03758056299784</v>
+      </c>
+      <c r="X12" t="n">
+        <v>23.97346914860318</v>
       </c>
     </row>
     <row r="13">
@@ -10470,10 +10790,10 @@
         <v>99.1861239547322</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>28.80245418851694</v>
+        <v>221.5849768170285</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>39.30531307022012</v>
+        <v>947.0948277574396</v>
       </c>
       <c r="G13" s="2" t="n">
         <v>303.8057015764734</v>
@@ -10522,6 +10842,12 @@
       </c>
       <c r="V13" s="2" t="n">
         <v>406.0871436305475</v>
+      </c>
+      <c r="W13" t="n">
+        <v>28.76308884060976</v>
+      </c>
+      <c r="X13" t="n">
+        <v>39.23752949114421</v>
       </c>
     </row>
     <row r="14">
@@ -10540,10 +10866,10 @@
         <v>57.63885649831866</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>19.36885639926595</v>
+        <v>117.1076353098614</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>32.69415488144099</v>
+        <v>512.5799827947337</v>
       </c>
       <c r="G14" s="2" t="n">
         <v>196.0520754129374</v>
@@ -10592,6 +10918,12 @@
       </c>
       <c r="V14" s="2" t="n">
         <v>269.9119415904116</v>
+      </c>
+      <c r="W14" t="n">
+        <v>19.34550815905992</v>
+      </c>
+      <c r="X14" t="n">
+        <v>32.6398139702783</v>
       </c>
     </row>
     <row r="15">
@@ -10610,10 +10942,10 @@
         <v>258.3713541792175</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>57.99352042215541</v>
+        <v>682.3973168995113</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>133.3645545250341</v>
+        <v>12693.728405856</v>
       </c>
       <c r="G15" s="2" t="n">
         <v>289.5633692796501</v>
@@ -10662,6 +10994,12 @@
       </c>
       <c r="V15" s="2" t="n">
         <v>444.5706447547481</v>
+      </c>
+      <c r="W15" t="n">
+        <v>57.89776466431431</v>
+      </c>
+      <c r="X15" t="n">
+        <v>133.0290935791215</v>
       </c>
     </row>
     <row r="16">
@@ -10680,10 +11018,10 @@
         <v>107.184597272732</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>30.48253250849711</v>
+        <v>242.7231196463857</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>47.0259883288617</v>
+        <v>1189.135083047449</v>
       </c>
       <c r="G16" s="2" t="n">
         <v>195.3372270916634</v>
@@ -10732,6 +11070,12 @@
       </c>
       <c r="V16" s="2" t="n">
         <v>249.53562033654</v>
+      </c>
+      <c r="W16" t="n">
+        <v>30.44016856732753</v>
+      </c>
+      <c r="X16" t="n">
+        <v>46.93975457748277</v>
       </c>
     </row>
     <row r="17">
@@ -10750,10 +11094,10 @@
         <v>94.89020727664703</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>27.88511775272285</v>
+        <v>210.3528549204131</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>45.03806849341223</v>
+        <v>1121.780149892512</v>
       </c>
       <c r="G17" s="2" t="n">
         <v>129.3193046916342</v>
@@ -10802,6 +11146,12 @@
       </c>
       <c r="V17" s="2" t="n">
         <v>199.476508548944</v>
+      </c>
+      <c r="W17" t="n">
+        <v>27.8473729981765</v>
+      </c>
+      <c r="X17" t="n">
+        <v>44.95489195220384</v>
       </c>
     </row>
     <row r="18">
@@ -10820,10 +11170,10 @@
         <v>289.7876734589325</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>63.06811537136963</v>
+        <v>780.8845872970606</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>123.631482963851</v>
+        <v>6729.572839285409</v>
       </c>
       <c r="G18" s="2" t="n">
         <v>635.8737662720922</v>
@@ -10872,6 +11222,12 @@
       </c>
       <c r="V18" s="2" t="n">
         <v>997.5740475825862</v>
+      </c>
+      <c r="W18" t="n">
+        <v>62.96183117057813</v>
+      </c>
+      <c r="X18" t="n">
+        <v>123.3440906020121</v>
       </c>
     </row>
     <row r="19">
@@ -10890,10 +11246,10 @@
         <v>167.9268901447387</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>42.32427293966179</v>
+        <v>411.3330540590173</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>81.56408529214163</v>
+        <v>4421.558639851675</v>
       </c>
       <c r="G19" s="2" t="n">
         <v>424.4204120084829</v>
@@ -10942,6 +11298,12 @@
       </c>
       <c r="V19" s="2" t="n">
         <v>594.4319588755127</v>
+      </c>
+      <c r="W19" t="n">
+        <v>42.25980631304412</v>
+      </c>
+      <c r="X19" t="n">
+        <v>81.38230125747123</v>
       </c>
     </row>
     <row r="20">
@@ -10960,10 +11322,10 @@
         <v>201.3110327290003</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>48.32309556834325</v>
+        <v>508.9912364824458</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>84.45663634494716</v>
+        <v>3291.343690486387</v>
       </c>
       <c r="G20" s="2" t="n">
         <v>203.6989805411893</v>
@@ -11012,6 +11374,12 @@
       </c>
       <c r="V20" s="2" t="n">
         <v>276.4589585725923</v>
+      </c>
+      <c r="W20" t="n">
+        <v>48.24688898293754</v>
+      </c>
+      <c r="X20" t="n">
+        <v>84.27648247438202</v>
       </c>
     </row>
     <row r="21">
@@ -11030,10 +11398,10 @@
         <v>536.3996649668767</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>98.92105285427314</v>
+        <v>1609.730472625195</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>192.0354449831898</v>
+        <v>13598.16488141827</v>
       </c>
       <c r="G21" s="2" t="n">
         <v>393.6118730166681</v>
@@ -11082,6 +11450,12 @@
       </c>
       <c r="V21" s="2" t="n">
         <v>627.3528167669332</v>
+      </c>
+      <c r="W21" t="n">
+        <v>98.73625924615786</v>
+      </c>
+      <c r="X21" t="n">
+        <v>191.5559801475918</v>
       </c>
     </row>
     <row r="22">
@@ -11100,10 +11474,10 @@
         <v>536.6382306190739</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>98.95321215930086</v>
+        <v>1610.571623171643</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>189.1980214024598</v>
+        <v>12376.73357180041</v>
       </c>
       <c r="G22" s="2" t="n">
         <v>525.0908437910632</v>
@@ -11152,6 +11526,12 @@
       </c>
       <c r="V22" s="2" t="n">
         <v>802.6979220092956</v>
+      </c>
+      <c r="W22" t="n">
+        <v>98.76834540849386</v>
+      </c>
+      <c r="X22" t="n">
+        <v>188.7299541478544</v>
       </c>
     </row>
     <row r="23">
@@ -11170,10 +11550,10 @@
         <v>336.3938507057656</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>70.33251350885153</v>
+        <v>930.4221122812825</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>96.95685657472633</v>
+        <v>2272.634239207302</v>
       </c>
       <c r="G23" s="2" t="n">
         <v>465.6307424829084</v>
@@ -11222,6 +11602,12 @@
       </c>
       <c r="V23" s="2" t="n">
         <v>1226.777069878792</v>
+      </c>
+      <c r="W23" t="n">
+        <v>70.21087184652784</v>
+      </c>
+      <c r="X23" t="n">
+        <v>96.76069753557947</v>
       </c>
     </row>
     <row r="24">
@@ -11240,10 +11626,10 @@
         <v>770.807846749354</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>128.9413282955242</v>
+        <v>2464.580714764936</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>238.8642044033908</v>
+        <v>23107.00660545965</v>
       </c>
       <c r="G24" s="2" t="n">
         <v>1197.942600408966</v>
@@ -11292,6 +11678,12 @@
       </c>
       <c r="V24" s="2" t="n">
         <v>1969.265633804265</v>
+      </c>
+      <c r="W24" t="n">
+        <v>128.6865723369627</v>
+      </c>
+      <c r="X24" t="n">
+        <v>238.2414834870946</v>
       </c>
     </row>
     <row r="25">
@@ -11310,10 +11702,10 @@
         <v>694.8941689734651</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>119.5298923502131</v>
+        <v>2181.937520325551</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>253.1629649309714</v>
+        <v>24146.03069088473</v>
       </c>
       <c r="G25" s="2" t="n">
         <v>1076.336205971309</v>
@@ -11362,6 +11754,12 @@
       </c>
       <c r="V25" s="2" t="n">
         <v>1880.403394533115</v>
+      </c>
+      <c r="W25" t="n">
+        <v>119.2974108495846</v>
+      </c>
+      <c r="X25" t="n">
+        <v>252.4893979315975</v>
       </c>
     </row>
     <row r="26">
@@ -11380,10 +11778,10 @@
         <v>663.7195178466512</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>115.5857987991034</v>
+        <v>2067.391179715494</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>193.9820464701548</v>
+        <v>14570.76074672779</v>
       </c>
       <c r="G26" s="2" t="n">
         <v>601.5468445458777</v>
@@ -11432,6 +11830,12 @@
       </c>
       <c r="V26" s="2" t="n">
         <v>994.6946215783587</v>
+      </c>
+      <c r="W26" t="n">
+        <v>115.3625637881615</v>
+      </c>
+      <c r="X26" t="n">
+        <v>193.5009343942022</v>
       </c>
     </row>
     <row r="27">
@@ -11450,10 +11854,10 @@
         <v>283.3262427405791</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>62.03702685919393</v>
+        <v>760.4687493012735</v>
       </c>
       <c r="F27" s="2" t="n">
-        <v>133.9962329328119</v>
+        <v>9080.748733909966</v>
       </c>
       <c r="G27" s="2" t="n">
         <v>410.4710283049905</v>
@@ -11502,6 +11906,12 @@
       </c>
       <c r="V27" s="2" t="n">
         <v>610.0540138948419</v>
+      </c>
+      <c r="W27" t="n">
+        <v>61.93289577099692</v>
+      </c>
+      <c r="X27" t="n">
+        <v>133.6701614106587</v>
       </c>
     </row>
     <row r="28">
@@ -11520,10 +11930,10 @@
         <v>158.4407803789103</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>40.56290610566914</v>
+        <v>384.1710875357484</v>
       </c>
       <c r="F28" s="2" t="n">
-        <v>69.14309272006736</v>
+        <v>2655.762506698117</v>
       </c>
       <c r="G28" s="2" t="n">
         <v>197.3866593685044</v>
@@ -11572,6 +11982,12 @@
       </c>
       <c r="V28" s="2" t="n">
         <v>271.3129782298061</v>
+      </c>
+      <c r="W28" t="n">
+        <v>40.50182298858382</v>
+      </c>
+      <c r="X28" t="n">
+        <v>68.99987341672315</v>
       </c>
     </row>
     <row r="29">
@@ -11590,10 +12006,10 @@
         <v>165.1796771222783</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>41.81699351005042</v>
+        <v>403.4385375229931</v>
       </c>
       <c r="F29" s="2" t="n">
-        <v>65.6922890975089</v>
+        <v>1806.275122137974</v>
       </c>
       <c r="G29" s="2" t="n">
         <v>290.5457815524936</v>
@@ -11642,6 +12058,12 @@
       </c>
       <c r="V29" s="2" t="n">
         <v>587.9816292505517</v>
+      </c>
+      <c r="W29" t="n">
+        <v>41.75350445389972</v>
+      </c>
+      <c r="X29" t="n">
+        <v>65.56164845420059</v>
       </c>
     </row>
     <row r="30">
@@ -11660,10 +12082,10 @@
         <v>33.25478525090308</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>12.95667542933245</v>
+        <v>61.37025533713454</v>
       </c>
       <c r="F30" s="2" t="n">
-        <v>23.99611880245712</v>
+        <v>361.2652457354941</v>
       </c>
       <c r="G30" s="2" t="n">
         <v>36.39332338325889</v>
@@ -11712,6 +12134,12 @@
       </c>
       <c r="V30" s="2" t="n">
         <v>42.0872231650101</v>
+      </c>
+      <c r="W30" t="n">
+        <v>12.94317451570484</v>
+      </c>
+      <c r="X30" t="n">
+        <v>23.95793731437822</v>
       </c>
     </row>
     <row r="31">
@@ -11730,10 +12158,10 @@
         <v>20.60629913269998</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>9.131659564304259</v>
+        <v>34.97513898062208</v>
       </c>
       <c r="F31" s="2" t="n">
-        <v>12.79079223465034</v>
+        <v>80.50966404685303</v>
       </c>
       <c r="G31" s="2" t="n">
         <v>20.32061106033339</v>
@@ -11782,6 +12210,12 @@
       </c>
       <c r="V31" s="2" t="n">
         <v>20.71483929978241</v>
+      </c>
+      <c r="W31" t="n">
+        <v>9.123443335229625</v>
+      </c>
+      <c r="X31" t="n">
+        <v>12.77580658762833</v>
       </c>
     </row>
     <row r="32">
@@ -11800,10 +12234,10 @@
         <v>39.81071705534973</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>14.77811807337469</v>
+        <v>75.81724064970111</v>
       </c>
       <c r="F32" s="2" t="n">
-        <v>19.53815724820203</v>
+        <v>140.2165385342558</v>
       </c>
       <c r="G32" s="2" t="n">
         <v>190.4040920716112</v>
@@ -11852,6 +12286,12 @@
       </c>
       <c r="V32" s="2" t="n">
         <v>198.8920305098167</v>
+      </c>
+      <c r="W32" t="n">
+        <v>14.76192892366971</v>
+      </c>
+      <c r="X32" t="n">
+        <v>19.51287980403976</v>
       </c>
     </row>
     <row r="33">
@@ -11870,10 +12310,10 @@
         <v>14.71217112194568</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>7.138150161957237</v>
+        <v>23.54240736127333</v>
       </c>
       <c r="F33" s="2" t="n">
-        <v>9.86572583660954</v>
+        <v>66.94570262780725</v>
       </c>
       <c r="G33" s="2" t="n">
         <v>14.79760102200063</v>
@@ -11922,6 +12362,12 @@
       </c>
       <c r="V33" s="2" t="n">
         <v>15.8112164443005</v>
+      </c>
+      <c r="W33" t="n">
+        <v>7.132442509188241</v>
+      </c>
+      <c r="X33" t="n">
+        <v>9.85463556313668</v>
       </c>
     </row>
     <row r="34">
@@ -11940,10 +12386,10 @@
         <v>15.81299528405932</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>7.524777705808002</v>
+        <v>25.62522809850928</v>
       </c>
       <c r="F34" s="2" t="n">
-        <v>11.75404832527506</v>
+        <v>117.6611600421435</v>
       </c>
       <c r="G34" s="2" t="n">
         <v>26.52199690564272</v>
@@ -11992,6 +12438,12 @@
       </c>
       <c r="V34" s="2" t="n">
         <v>27.58750158265776</v>
+      </c>
+      <c r="W34" t="n">
+        <v>7.518599497541913</v>
+      </c>
+      <c r="X34" t="n">
+        <v>11.73902826550227</v>
       </c>
     </row>
     <row r="35">
@@ -12010,10 +12462,10 @@
         <v>18.61708723298873</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>8.478531976146394</v>
+        <v>31.04288882388031</v>
       </c>
       <c r="F35" s="2" t="n">
-        <v>18.48000840404622</v>
+        <v>287.9969723030186</v>
       </c>
       <c r="G35" s="2" t="n">
         <v>140.2531467766166</v>
@@ -12062,6 +12514,12 @@
       </c>
       <c r="V35" s="2" t="n">
         <v>246.8718593298187</v>
+      </c>
+      <c r="W35" t="n">
+        <v>8.471159248049466</v>
+      </c>
+      <c r="X35" t="n">
+        <v>18.44967698338515</v>
       </c>
     </row>
     <row r="36">
@@ -12080,10 +12538,10 @@
         <v>10</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>5.38284603096072</v>
+        <v>14.95736128795635</v>
       </c>
       <c r="F36" s="2" t="n">
-        <v>5.38284603096072</v>
+        <v>14.95736128795635</v>
       </c>
       <c r="G36" s="2" t="n">
         <v>4.952947003467063</v>
@@ -12132,6 +12590,12 @@
       </c>
       <c r="V36" s="2" t="n">
         <v>5.002266311184844</v>
+      </c>
+      <c r="W36" t="n">
+        <v>5.379159769610195</v>
+      </c>
+      <c r="X36" t="n">
+        <v>5.379159769610195</v>
       </c>
     </row>
     <row r="37">
@@ -12150,10 +12614,10 @@
         <v>103.7909360953989</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>29.77396345132429</v>
+        <v>233.7195026604724</v>
       </c>
       <c r="F37" s="2" t="n">
-        <v>28.53269211364632</v>
+        <v>253.7361002571505</v>
       </c>
       <c r="G37" s="2" t="n">
         <v>147.8720821296587</v>
@@ -12202,6 +12666,12 @@
       </c>
       <c r="V37" s="2" t="n">
         <v>427.7277128735025</v>
+      </c>
+      <c r="W37" t="n">
+        <v>29.73286887071495</v>
+      </c>
+      <c r="X37" t="n">
+        <v>28.49200913915451</v>
       </c>
     </row>
     <row r="38">
@@ -12220,10 +12690,10 @@
         <v>10</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>5.38284603096072</v>
+        <v>14.95736128795635</v>
       </c>
       <c r="F38" s="2" t="n">
-        <v>5.382846030960719</v>
+        <v>14.95736128795635</v>
       </c>
       <c r="G38" s="2" t="n">
         <v>19.6078431372549</v>
@@ -12272,6 +12742,12 @@
       </c>
       <c r="V38" s="2" t="n">
         <v>20.2690018570508</v>
+      </c>
+      <c r="W38" t="n">
+        <v>5.379159769610195</v>
+      </c>
+      <c r="X38" t="n">
+        <v>5.379159769610194</v>
       </c>
     </row>
     <row r="39">
@@ -12343,6 +12819,12 @@
       <c r="V39" s="2" t="n">
         <v>1</v>
       </c>
+      <c r="W39" t="n">
+        <v>1</v>
+      </c>
+      <c r="X39" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
@@ -12411,6 +12893,12 @@
         <v>1</v>
       </c>
       <c r="V40" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="W40" t="n">
+        <v>1</v>
+      </c>
+      <c r="X40" t="n">
         <v>1</v>
       </c>
     </row>
@@ -12883,7 +13371,6 @@
           <t>WARN</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr"/>
       <c r="AD2" s="2" t="n">
         <v>0.00408138212364339</v>
       </c>
@@ -13009,7 +13496,6 @@
       <c r="H3" t="b">
         <v>0</v>
       </c>
-      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
           <t>South_China_Sea_SCS-2007_Northern_South_China_Sea (2000s)</t>
@@ -13073,7 +13559,6 @@
           <t>WARN</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr"/>
       <c r="AD3" s="2" t="n">
         <v>0</v>
       </c>
@@ -13267,7 +13752,6 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr"/>
       <c r="AD4" s="2" t="n">
         <v>0.004418657486753578</v>
       </c>
@@ -13369,7 +13853,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G21"/>
+  <dimension ref="A1:G23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -13430,14 +13914,12 @@
       <c r="C2" s="2" t="n">
         <v>490.8226543866692</v>
       </c>
-      <c r="D2" t="inlineStr"/>
       <c r="E2" s="2" t="n">
         <v>130373.17</v>
       </c>
       <c r="F2" s="2" t="n">
         <v>0.003764752014441846</v>
       </c>
-      <c r="G2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
@@ -13451,14 +13933,12 @@
       <c r="C3" s="2" t="n">
         <v>711.266414816086</v>
       </c>
-      <c r="D3" t="inlineStr"/>
       <c r="E3" s="2" t="n">
         <v>130373.17</v>
       </c>
       <c r="F3" s="2" t="n">
         <v>0.005455619548225191</v>
       </c>
-      <c r="G3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -13467,19 +13947,17 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>196.2297576267595</v>
+        <v>1688.653581098596</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>196.2297576267595</v>
-      </c>
-      <c r="D4" t="inlineStr"/>
+        <v>1688.653581098596</v>
+      </c>
       <c r="E4" s="2" t="n">
         <v>130373.17</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>0.001505139114334334</v>
-      </c>
-      <c r="G4" t="inlineStr"/>
+        <v>0.01295246239006535</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
@@ -13488,22 +13966,22 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>305.9222947439239</v>
+        <v>9464.629663113257</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>305.9222947439238</v>
+        <v>9464.629663113257</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>162.0067594021208</v>
+        <v>4807.988736275122</v>
       </c>
       <c r="E5" s="2" t="n">
         <v>130373.17</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>0.002346512666248154</v>
+        <v>0.07259645265289827</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>0.001242638799088193</v>
+        <v>0.03687866710823341</v>
       </c>
     </row>
     <row r="6">
@@ -13904,6 +14382,50 @@
       </c>
       <c r="G21" s="2" t="n">
         <v>0.008671983107106327</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>SPPR_1995_TEmean_catch</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>195.9560923237997</v>
+      </c>
+      <c r="C22" t="n">
+        <v>195.9560923237997</v>
+      </c>
+      <c r="E22" t="n">
+        <v>130373.17</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0.001503040022144125</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Ulanowicz_globalTEmean_catch</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>305.35238230975</v>
+      </c>
+      <c r="C23" t="n">
+        <v>305.35238230975</v>
+      </c>
+      <c r="D23" t="n">
+        <v>161.7104934662456</v>
+      </c>
+      <c r="E23" t="n">
+        <v>130373.17</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0.002342141272700127</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0.001240366353493173</v>
       </c>
     </row>
   </sheetData>
@@ -14039,7 +14561,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C30"/>
+  <dimension ref="A1:C32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -14075,7 +14597,6 @@
           <t>NaN means not available, never zero. A basal source a method does not resolve is NaN, and a method that raised leaves its entire block NaN.</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
@@ -14088,7 +14609,6 @@
           <t>sppr_all, sppr_inner and sppr_PP are the same table under three source scopes, mirroring get_PPR: sppr_all sums every basal source, sppr_inner drops Import, and sppr_PP drops Import and Detritus. Each is a flat groups x methods table -- rows are group seq with the group name in the first column, one column per method, no MultiIndex. Sums are taken over each method's own basal-source columns before aggregation; the per-source breakdown itself is not written to the workbook.</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -14101,7 +14621,6 @@
           <t>SPPR_1986 and SPPR_1995 return one un-attributed SPPR column, so their value cannot be split into a PP-only part: they are NaN in sppr_PP (and in ppr_pp_only) while sppr_inner and sppr_all carry the total. A method that resolves no Detritus source (SPPR_2015) has sppr_inner equal to sppr_PP by construction.</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
@@ -14114,7 +14633,6 @@
           <t>SPPR_2015() has no only_pp_det parameter (only_pp belongs to get_PPR / get_PPR2NPP_ratio). It is called bare here and PP-only filtering is applied downstream at the get_PPR layer, which is what the ppr_pp_only column and SUM_PP already do.</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
@@ -14127,7 +14645,6 @@
           <t>Under det_open_mode='none' det_theta does not affect the recycling gain b at all (verified: identical b at theta = 1, 3 and 10). Do not read the health sheet as a theta sensitivity.</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
@@ -14140,7 +14657,6 @@
           <t>MC runs use exclude_diverged=True, so draws graded FAIL on divergence are dropped as well as draws with a negative SPPR. The two are often the same draws rather than additive -- see the mc_diagnostics sheet for the split by cause.</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
@@ -14153,7 +14669,6 @@
           <t>SPPR_EwE and the Monte-Carlo methods are called with silent=True rather than silent=False: PPRCalculator imports tqdm.notebook, whose bar needs ipywidgets and raises ImportError('IProgress not found') outside Jupyter, which makes those methods fail outright in a terminal run. Nothing is lost -- this exporter has its own progress bar, and the MC rejection counts appear in mc_diagnostics and in the run report.</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
@@ -14166,7 +14681,6 @@
           <t>diagnose_sppr grades a CONFIGURATION, not a model: a model can be healthy under one TE_option and divergent under another. Read each row with its config_ columns.</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
@@ -14179,7 +14693,6 @@
           <t>Every SPPR method, and every diagnose_sppr row, runs in a worker process with a wall-clock budget (180 s by default; --timeout SECONDS on the command line, method_timeout= from Python, and None or 0 to disable it). A method still running when the budget expires is killed and left NaN, exactly like a method that raised -- the status column of this sheet and the run report are the only places that say which of the two happened. A timeout is a statement about this machine and this model, not about the method: rerun it with a larger budget before reading anything into it.</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
@@ -14223,7 +14736,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Pauly &amp; Christensen (1995): per-group TE^(1-TL) with global_TE='mean'.</t>
+          <t>Pauly &amp; Christensen (1995): per-group TE^(1-TL) with global_TE='mean'. Arithmetic mean with consumer consumption weights.</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -14240,7 +14753,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Nullspace form of the EwE path sum, global TE at the true mean (Jensen-able on TL).</t>
+          <t>Nullspace form of the EwE path sum, global TE at the consumer consumption-weighted arithmetic mean (Jensen-able on TL).</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -14516,6 +15029,40 @@
         </is>
       </c>
       <c r="C30" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>method: SPPR_1995_TEmean_catch</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Pauly &amp; Christensen (1995): per-group TE^(1-TL) with global_TE='mean'. Arithmetic mean with consumer catch weights. Consumer biomass fallback when consumer catch is zero.</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>method: Ulanowicz_globalTEmean_catch</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Nullspace form of the EwE path sum, global TE at the consumer catch-weighted arithmetic mean. Consumer biomass fallback when consumer catch is zero (Jensen-able on TL).</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
